--- a/data/merged/2026-09-28/MERGED_UK_Stick-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_UK_Stick-Vacuum_2026-09-28.xlsx
@@ -7328,13 +7328,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7372,13 +7372,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7416,13 +7416,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7807,50 +7807,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8176,7 +8132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -18003,275 +17959,35 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0F9YPP9C3</t>
-        </is>
-      </c>
-      <c r="D40" s="14"/>
+          <t>B0H2J8QH51</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Colour Name: Black</t>
+        </is>
+      </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Brand: Shark | Colour: White | Product dimensions: 9.9L x 15.5W x 25.4H centimetres | Surface recommendation: Floor | Item weight: 0.55 Kilograms</t>
+          <t>Brand: VACTechPro | Special feature: 40Kpa/50Mins/450W, 8-Layer Cyclonic Dust Separation System, Self Standing Design &amp; Lightweight, Smart Corner Light Design, Upgraded Anti-Tangle System | Filter type: HEPA Filter | Surface recommendation: Hard Floor, Carpet, Hardwood, Car | Included components: Battery</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>VACTechPro</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0F9YPP9C3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Shark Disposable Hard Floor Vacuum and Mop Pad VACMOP Refill 16 Pack, White</t>
+          <t>VACTechPro F02 Lite Cordless Vacuum Cleaner, 40KPa/450W, Self-Standing</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>Shark Mop Pad VACMOP Refill 16 Pack: Designed for use with Shark VacMop Cordless VM200UK, VM200UKGL, and VM200UKPL
-The VACMOP Pad vacuums up and locks away debris in an innovative built-in dirt chamber
-Featuring absorbent mopping layers to clean stuck-on grime—providing shiny clean floors
-Easy replacement ensures a fresh, like-new clean every time
-For use on ALL sealed floors—stone, hardwood, vinyl, laminate, tile, marble, and linoleum</t>
-        </is>
-      </c>
-      <c r="J40" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1</t>
-        </is>
-      </c>
-      <c r="K40" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L40" s="14" t="inlineStr">
-        <is>
-          <t>B0F9YPP9C3</t>
-        </is>
-      </c>
-      <c r="M40" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="N40" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O40" s="15">
-        <v>1089</v>
-      </c>
-      <c r="P40" s="15">
-        <v>146</v>
-      </c>
-      <c r="Q40" s="16">
-        <v>0.11</v>
-      </c>
-      <c r="R40" s="17" t="inlineStr">
-        <is>
-          <t>Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="S40" s="18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T40" s="15">
-        <v>2044</v>
-      </c>
-      <c r="U40" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="V40" s="15">
-        <v>30640</v>
-      </c>
-      <c r="W40" s="15" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="X40" s="15">
-        <v>14990</v>
-      </c>
-      <c r="Y40" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="20">
-        <v>12.49</v>
-      </c>
-      <c r="AA40" s="4"/>
-      <c r="AB40" s="1"/>
-      <c r="AC40" s="2"/>
-      <c r="AD40" s="19">
-        <v>188</v>
-      </c>
-      <c r="AE40" s="15">
-        <v>10</v>
-      </c>
-      <c r="AF40" s="21">
-        <v>4.7</v>
-      </c>
-      <c r="AG40" s="22">
-        <v>0.0049</v>
-      </c>
-      <c r="AH40" s="20">
-        <v>3.2</v>
-      </c>
-      <c r="AI40" s="16">
-        <v>0.79</v>
-      </c>
-      <c r="AJ40"/>
-      <c r="AK40" s="13" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AL40" s="19">
-        <v>488</v>
-      </c>
-      <c r="AM40" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN40" s="13" t="inlineStr">
-        <is>
-          <t>9天</t>
-        </is>
-      </c>
-      <c r="AO40" s="13"/>
-      <c r="AP40" s="4">
-        <v>14.7</v>
-      </c>
-      <c r="AQ40" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR40" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS40" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT40" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU40" s="13"/>
-      <c r="AV40" s="14"/>
-      <c r="AW40" s="13"/>
-      <c r="AX40" s="13"/>
-      <c r="AY40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ40" s="13"/>
-      <c r="BA40" s="13"/>
-      <c r="BB40" s="13"/>
-      <c r="BC40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE40" s="13"/>
-      <c r="BF40" s="13"/>
-      <c r="BG40" s="13"/>
-      <c r="BH40" s="14"/>
-      <c r="BI40" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ40" s="23" t="inlineStr">
-        <is>
-          <t>0.55 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK40" s="23" t="inlineStr">
-        <is>
-          <t>550.00 g</t>
-        </is>
-      </c>
-      <c r="BL40" s="23" t="inlineStr">
-        <is>
-          <t>9.9L x 15.5W x 25.4H centimetres</t>
-        </is>
-      </c>
-      <c r="BM40" s="23"/>
-      <c r="BN40" s="23" t="inlineStr">
-        <is>
-          <t>550 g</t>
-        </is>
-      </c>
-      <c r="BO40" s="23" t="inlineStr">
-        <is>
-          <t>550.00 g</t>
-        </is>
-      </c>
-      <c r="BP40" s="23" t="inlineStr">
-        <is>
-          <t>26 x 16 x 16 cm</t>
-        </is>
-      </c>
-      <c r="BQ40" s="23" t="inlineStr">
-        <is>
-          <t>26.00 x 16.00 x 16.00 cm</t>
-        </is>
-      </c>
-      <c r="BR40" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13">
-        <v>40</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>B0H2J8QH51</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>Colour Name: Black</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Brand: VACTechPro | Special feature: 40Kpa/50Mins/450W, 8-Layer Cyclonic Dust Separation System, Self Standing Design &amp; Lightweight, Smart Corner Light Design, Upgraded Anti-Tangle System | Filter type: HEPA Filter | Surface recommendation: Hard Floor, Carpet, Hardwood, Car | Included components: Battery</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>VACTechPro</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>VACTechPro F02 Lite Cordless Vacuum Cleaner, 40KPa/450W, Self-Standing</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>40Kpa/450W Powerful Suction: VACTechPro F02 Lite cordless vacuum cleaner features a 120,000 RPM high-speed motor and an optimized airflow channel, providing 450W of power and 40KPa of suction. It is designed to quickly and easily clean up food crumbs, cat litter, pet hair, and grain particles.
 Self Standing Design: The floor nozzle of this cordless vacuum cleaner has a self-standing design, which allows the unit to remain upright on flat surfaces when not in use. This can be useful if you need to pause cleaning to attend to other tasks, as it reduces the need to lean the vacuum against furniture or bend down frequently to pick it up.
@@ -18282,19 +17998,261 @@
 8-Layer Cyclonic Dust Separation System: This vacuum features an 8-stage cyclone system that separates large debris and fine dust from the air, directing them into the dust compartment. This reduces dust reaching the HEPA filter, meaning less frequent filter cleaning and more consistent suction over time.</t>
         </is>
       </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41LbZ7ZgbSL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L40" s="14" t="inlineStr">
+        <is>
+          <t>B0HJ532G15</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
+        <is>
+          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
+        </is>
+      </c>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>Home &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="O40" s="15">
+        <v>10055</v>
+      </c>
+      <c r="P40" s="15">
+        <v>66783</v>
+      </c>
+      <c r="Q40" s="16">
+        <v>0.93</v>
+      </c>
+      <c r="R40" s="17" t="inlineStr">
+        <is>
+          <t>Stick Vacuums &amp; Electric Brooms</t>
+        </is>
+      </c>
+      <c r="S40" s="18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="T40" s="15">
+        <v>308</v>
+      </c>
+      <c r="U40" s="16">
+        <v>-0.09</v>
+      </c>
+      <c r="V40" s="15">
+        <v>24637</v>
+      </c>
+      <c r="W40" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X40" s="15">
+        <v>4000</v>
+      </c>
+      <c r="Y40" s="19">
+        <v>5</v>
+      </c>
+      <c r="Z40" s="20">
+        <v>79.99</v>
+      </c>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="2"/>
+      <c r="AD40" s="19">
+        <v>29</v>
+      </c>
+      <c r="AE40" s="15">
+        <v>36</v>
+      </c>
+      <c r="AF40" s="21">
+        <v>4.7</v>
+      </c>
+      <c r="AG40" s="22">
+        <v>0.11689999999999999</v>
+      </c>
+      <c r="AH40" s="20">
+        <v>3.71</v>
+      </c>
+      <c r="AI40" s="16">
+        <v>0.95</v>
+      </c>
+      <c r="AJ40"/>
+      <c r="AK40" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AL40" s="19">
+        <v>101</v>
+      </c>
+      <c r="AM40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN40" s="13"/>
+      <c r="AO40" s="13"/>
+      <c r="AP40" s="4"/>
+      <c r="AQ40" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR40" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS40" s="14" t="inlineStr">
+        <is>
+          <t>HUIZHENG TECO</t>
+        </is>
+      </c>
+      <c r="AT40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU40" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV40" s="14" t="inlineStr">
+        <is>
+          <t>WAN CHAI 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW40" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN</t>
+        </is>
+      </c>
+      <c r="AX40" s="13"/>
+      <c r="AY40" s="13"/>
+      <c r="AZ40" s="13"/>
+      <c r="BA40" s="13"/>
+      <c r="BB40" s="13"/>
+      <c r="BC40" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD40" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE40" s="13"/>
+      <c r="BF40" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG40" s="13"/>
+      <c r="BH40" s="14"/>
+      <c r="BI40" s="23"/>
+      <c r="BJ40" s="23" t="inlineStr">
+        <is>
+          <t>3.24 kg</t>
+        </is>
+      </c>
+      <c r="BK40" s="23" t="inlineStr">
+        <is>
+          <t>3.24 kg</t>
+        </is>
+      </c>
+      <c r="BL40" s="23" t="inlineStr">
+        <is>
+          <t>35L x 15W x 22H centimetres</t>
+        </is>
+      </c>
+      <c r="BM40" s="23"/>
+      <c r="BN40" s="23" t="inlineStr">
+        <is>
+          <t>3.24 kg</t>
+        </is>
+      </c>
+      <c r="BO40" s="23" t="inlineStr">
+        <is>
+          <t>3.24 kg</t>
+        </is>
+      </c>
+      <c r="BP40" s="23" t="inlineStr">
+        <is>
+          <t>40.1 x 27.6 x 18.4 cm</t>
+        </is>
+      </c>
+      <c r="BQ40" s="23" t="inlineStr">
+        <is>
+          <t>40.10 x 27.60 x 18.40 cm</t>
+        </is>
+      </c>
+      <c r="BR40" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
+        <v>40</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>B09RMQ1XLL</t>
+        </is>
+      </c>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Brand: VYTRONIX | Special feature: Compact, Portable, Washable Filter | Filter type: HEPA Filter | Surface recommendation: Carpet, Hard Floor | Power source: Corded Electric</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>VYTRONIX</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>VYTRONIX HSV3 Upright Vacuum Cleaner | Lightweight 3-in-1 Compact Powerful Multifunction Corded Stick &amp; Handheld Vacuum | 600 Watt, 5 Metre Power Cord | 2.5Kg</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>GET THE JOB DONE: We created the HSV3 3-in-1 corded stick vacuum cleaner to help you power through your housework so you can get back to life. It has all the features of a handheld vacuum but with the added benefit of a floorhead attachment, telescopic extension tube and no need to charge
+EFFORTLESS CLEANING: The detachable crevice/dusting tool and 5m cord are perfect for getting into nooks and crannies. The easy-to-use rocker pedal on the floor head allows you to conveniently switch between carpet and hard floor modes. Easily release the 0.8 litre dust canister into the bin with the “one-click” emptying system
+MICRO FILTRATION: With its powerful corded design and cyclonic technology, you can be sure that you’re picking up even the most invisible dust and dirt particles and eliminating them from the air. The microfilter traps dust, pet hair, and other allergens - perfect for alleviating allergy symptoms
+COMPACT &amp; AGILE: This Vytronix vacuum cleaner is as efficient as it is mobile. At just 2.5 kg, you can easily carry it wherever you clean, whether it’s room to room, sofas or up and down the stairs. Once the job is done, wash the filter, detach the attachments and store. Product dimensions are 31 x 11 x 21cm
+POWERFULLY SIMPLE: We like to keep it simple. How? By creating home appliances that get the job done, brilliantly. No frills, no gimmicks and no features you’ll never use. They're also built to last, so to give you complete peace of mind they also come with a 1 year guarantee.</t>
+        </is>
+      </c>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41LbZ7ZgbSL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0HJ532G15</t>
+          <t>B09RMQ1XLL</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -18308,13 +18266,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>10055</v>
+        <v>3301</v>
       </c>
       <c r="P41" s="15">
-        <v>66783</v>
+        <v>2421</v>
       </c>
       <c r="Q41" s="16">
-        <v>0.93</v>
+        <v>0.41</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -18323,61 +18281,61 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>308</v>
+        <v>740</v>
       </c>
       <c r="U41" s="16">
-        <v>-0.09</v>
+        <v>0.41</v>
       </c>
       <c r="V41" s="15">
-        <v>24637</v>
+        <v>24413</v>
       </c>
       <c r="W41" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>600</t>
         </is>
       </c>
       <c r="X41" s="15">
-        <v>4000</v>
+        <v>19794</v>
       </c>
       <c r="Y41" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>79.99</v>
+        <v>32.99</v>
       </c>
       <c r="AA41" s="4"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="19">
-        <v>29</v>
+        <v>4166</v>
       </c>
       <c r="AE41" s="15">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="AF41" s="21">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.11689999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="AH41" s="20">
-        <v>3.71</v>
+        <v>4.87</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>101</v>
+        <v>1685</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
@@ -18391,11 +18349,11 @@
         <v>10</v>
       </c>
       <c r="AR41" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>HUIZHENG TECO</t>
+          <t>Vytronix</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
@@ -18405,21 +18363,25 @@
       </c>
       <c r="AU41" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV41" s="14" t="inlineStr">
         <is>
-          <t>WAN CHAI 999077 HK</t>
+          <t>Dunstable Bedfordshire LU5 5UL GB</t>
         </is>
       </c>
       <c r="AW41" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
         </is>
       </c>
       <c r="AX41" s="13"/>
-      <c r="AY41" s="13"/>
+      <c r="AY41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ41" s="13"/>
       <c r="BA41" s="13"/>
       <c r="BB41" s="13"/>
@@ -18428,59 +18390,55 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD41" s="13"/>
       <c r="BE41" s="13"/>
-      <c r="BF41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
       <c r="BH41" s="14"/>
-      <c r="BI41" s="23"/>
+      <c r="BI41" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.5 Kilograms</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>35L x 15W x 22H centimetres</t>
+          <t>21L x 11W x 31H centimetres</t>
         </is>
       </c>
       <c r="BM41" s="23"/>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.71 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.71 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>40.1 x 27.6 x 18.4 cm</t>
+          <t>46 x 23.1 x 16.5 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>40.10 x 27.60 x 18.40 cm</t>
+          <t>46.00 x 23.10 x 16.50 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18491,277 +18449,35 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B09RMQ1XLL</t>
-        </is>
-      </c>
-      <c r="D42" s="14"/>
+          <t>B0H1WC1PJ1</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Colour Name: Black Gold | Size Name: M</t>
+        </is>
+      </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Brand: VYTRONIX | Special feature: Compact, Portable, Washable Filter | Filter type: HEPA Filter | Surface recommendation: Carpet, Hard Floor | Power source: Corded Electric</t>
+          <t>Brand: Proscenic | Special feature: Cordless, Detachable Battery, HEPA, Headlight, Lightweight | Filter type: HEPA Filter | Surface recommendation: floor, carpet, pet hair | Power source: Battery Powered</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX</t>
+          <t>Proscenic</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/PROSCENIC/page/9D6AA08D-8BCB-40F7-A698-933D705EEDDF?lp_asin=B0H1WC1PJ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX HSV3 Upright Vacuum Cleaner | Lightweight 3-in-1 Compact Powerful Multifunction Corded Stick &amp; Handheld Vacuum | 600 Watt, 5 Metre Power Cord | 2.5Kg</t>
+          <t>Proscenic P15+ Cordless Vacuum Cleaner, 70Kpa, 70-Minute Runtime, Pet Hair</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>GET THE JOB DONE: We created the HSV3 3-in-1 corded stick vacuum cleaner to help you power through your housework so you can get back to life. It has all the features of a handheld vacuum but with the added benefit of a floorhead attachment, telescopic extension tube and no need to charge
-EFFORTLESS CLEANING: The detachable crevice/dusting tool and 5m cord are perfect for getting into nooks and crannies. The easy-to-use rocker pedal on the floor head allows you to conveniently switch between carpet and hard floor modes. Easily release the 0.8 litre dust canister into the bin with the “one-click” emptying system
-MICRO FILTRATION: With its powerful corded design and cyclonic technology, you can be sure that you’re picking up even the most invisible dust and dirt particles and eliminating them from the air. The microfilter traps dust, pet hair, and other allergens - perfect for alleviating allergy symptoms
-COMPACT &amp; AGILE: This Vytronix vacuum cleaner is as efficient as it is mobile. At just 2.5 kg, you can easily carry it wherever you clean, whether it’s room to room, sofas or up and down the stairs. Once the job is done, wash the filter, detach the attachments and store. Product dimensions are 31 x 11 x 21cm
-POWERFULLY SIMPLE: We like to keep it simple. How? By creating home appliances that get the job done, brilliantly. No frills, no gimmicks and no features you’ll never use. They're also built to last, so to give you complete peace of mind they also come with a 1 year guarantee.</t>
-        </is>
-      </c>
-      <c r="J42" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1</t>
-        </is>
-      </c>
-      <c r="K42" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L42" s="14" t="inlineStr">
-        <is>
-          <t>B09RMQ1XLL</t>
-        </is>
-      </c>
-      <c r="M42" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="N42" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O42" s="15">
-        <v>3301</v>
-      </c>
-      <c r="P42" s="15">
-        <v>2421</v>
-      </c>
-      <c r="Q42" s="16">
-        <v>0.41</v>
-      </c>
-      <c r="R42" s="17" t="inlineStr">
-        <is>
-          <t>Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="S42" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="T42" s="15">
-        <v>740</v>
-      </c>
-      <c r="U42" s="16">
-        <v>0.41</v>
-      </c>
-      <c r="V42" s="15">
-        <v>24413</v>
-      </c>
-      <c r="W42" s="15" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="X42" s="15">
-        <v>19794</v>
-      </c>
-      <c r="Y42" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z42" s="20">
-        <v>32.99</v>
-      </c>
-      <c r="AA42" s="4"/>
-      <c r="AB42" s="1"/>
-      <c r="AC42" s="2"/>
-      <c r="AD42" s="19">
-        <v>4166</v>
-      </c>
-      <c r="AE42" s="15">
-        <v>7</v>
-      </c>
-      <c r="AF42" s="21">
-        <v>4.1</v>
-      </c>
-      <c r="AG42" s="22">
-        <v>0.0095</v>
-      </c>
-      <c r="AH42" s="20">
-        <v>4.87</v>
-      </c>
-      <c r="AI42" s="16">
-        <v>0.85</v>
-      </c>
-      <c r="AJ42"/>
-      <c r="AK42" s="13" t="inlineStr">
-        <is>
-          <t>2022-02-16</t>
-        </is>
-      </c>
-      <c r="AL42" s="19">
-        <v>1685</v>
-      </c>
-      <c r="AM42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN42" s="13"/>
-      <c r="AO42" s="13"/>
-      <c r="AP42" s="4"/>
-      <c r="AQ42" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR42" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS42" s="14" t="inlineStr">
-        <is>
-          <t>Vytronix</t>
-        </is>
-      </c>
-      <c r="AT42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU42" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV42" s="14" t="inlineStr">
-        <is>
-          <t>Dunstable Bedfordshire LU5 5UL GB</t>
-        </is>
-      </c>
-      <c r="AW42" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
-        </is>
-      </c>
-      <c r="AX42" s="13"/>
-      <c r="AY42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ42" s="13"/>
-      <c r="BA42" s="13"/>
-      <c r="BB42" s="13"/>
-      <c r="BC42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD42" s="13"/>
-      <c r="BE42" s="13"/>
-      <c r="BF42" s="13"/>
-      <c r="BG42" s="13"/>
-      <c r="BH42" s="14"/>
-      <c r="BI42" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ42" s="23" t="inlineStr">
-        <is>
-          <t>2.5 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK42" s="23" t="inlineStr">
-        <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
-      <c r="BL42" s="23" t="inlineStr">
-        <is>
-          <t>21L x 11W x 31H centimetres</t>
-        </is>
-      </c>
-      <c r="BM42" s="23"/>
-      <c r="BN42" s="23" t="inlineStr">
-        <is>
-          <t>2.71 kg</t>
-        </is>
-      </c>
-      <c r="BO42" s="23" t="inlineStr">
-        <is>
-          <t>2.71 kg</t>
-        </is>
-      </c>
-      <c r="BP42" s="23" t="inlineStr">
-        <is>
-          <t>46 x 23.1 x 16.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ42" s="23" t="inlineStr">
-        <is>
-          <t>46.00 x 23.10 x 16.50 cm</t>
-        </is>
-      </c>
-      <c r="BR42" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="13">
-        <v>42</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>B0H1WC1PJ1</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>Colour Name: Black Gold | Size Name: M</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Brand: Proscenic | Special feature: Cordless, Detachable Battery, HEPA, Headlight, Lightweight | Filter type: HEPA Filter | Surface recommendation: floor, carpet, pet hair | Power source: Battery Powered</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>Proscenic</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/PROSCENIC/page/9D6AA08D-8BCB-40F7-A698-933D705EEDDF?lp_asin=B0H1WC1PJ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>Proscenic P15+ Cordless Vacuum Cleaner, 70Kpa, 70-Minute Runtime, Pet Hair</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
         <is>
           <t>【70kPa 600W Super Strong Suction】With its 600W brushless motor, the cordless vacuum delivers strong 70kPa suction to easily clean large debris, stubborn stains, pet hair, and hidden dust in corners and hard-to-reach areas. A perfect balance of power and convenience in a stick vacuum design
 【70-Minute Long Runtime】The lightweight hoover features a 2200mAh 8-cell battery, offering 70 minutes of continuous runtime on low mode—enough to clean a 250㎡ home on one charge. A spare battery (sold separately) ensures your cordless hoover never runs out of power mid-clean
@@ -18772,242 +18488,242 @@
 【After-Sales Service】Proscenic provides professional technical support and online customer service with rapid response within 24 hours. For any product-related questions or concerns, please contact us directly at any time—our support team is always here to assist you. Upgrade to Proscenic “All-in-One” vacuum cleaner today and simplify cleaning with unmatched powerful performance and reliable operation</t>
         </is>
       </c>
-      <c r="J43" s="14" t="inlineStr">
+      <c r="J42" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/dp/B0H1WC1PJ1?psc=1</t>
         </is>
       </c>
-      <c r="K43" s="14" t="inlineStr">
+      <c r="K42" s="14" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/61xgSdYZzpL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L43" s="14" t="inlineStr">
+      <c r="L42" s="14" t="inlineStr">
         <is>
           <t>B0HFJ14KF6</t>
         </is>
       </c>
-      <c r="M43" s="14" t="inlineStr">
+      <c r="M42" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="N43" s="14" t="inlineStr">
+      <c r="N42" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O43" s="15">
+      <c r="O42" s="15">
         <v>15339</v>
       </c>
-      <c r="P43" s="15">
+      <c r="P42" s="15">
         <v>-4225</v>
       </c>
-      <c r="Q43" s="16">
+      <c r="Q42" s="16">
         <v>-0.22</v>
       </c>
-      <c r="R43" s="17" t="inlineStr">
+      <c r="R42" s="17" t="inlineStr">
         <is>
           <t>Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="S43" s="18" t="inlineStr">
+      <c r="S42" s="18" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="T43" s="15">
+      <c r="T42" s="15">
         <v>187</v>
       </c>
-      <c r="U43" s="16">
+      <c r="U42" s="16">
         <v>-0.21</v>
       </c>
-      <c r="V43" s="15">
+      <c r="V42" s="15">
         <v>20568</v>
       </c>
-      <c r="W43" s="15" t="inlineStr">
+      <c r="W42" s="15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="X43" s="15">
+      <c r="X42" s="15">
         <v>10907</v>
       </c>
-      <c r="Y43" s="19">
+      <c r="Y42" s="19">
         <v>2</v>
       </c>
-      <c r="Z43" s="20">
+      <c r="Z42" s="20">
         <v>109.99</v>
       </c>
-      <c r="AA43" s="4"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="2"/>
-      <c r="AD43" s="19">
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="2"/>
+      <c r="AD42" s="19">
         <v>23</v>
       </c>
-      <c r="AE43" s="15">
+      <c r="AE42" s="15">
         <v>0</v>
       </c>
-      <c r="AF43" s="21">
+      <c r="AF42" s="21">
         <v>4.4</v>
       </c>
-      <c r="AG43" s="22">
+      <c r="AG42" s="22">
         <v>0</v>
       </c>
-      <c r="AH43" s="20">
+      <c r="AH42" s="20">
         <v>3.71</v>
       </c>
-      <c r="AI43" s="16">
+      <c r="AI42" s="16">
         <v>0.97</v>
       </c>
-      <c r="AJ43"/>
-      <c r="AK43" s="13" t="inlineStr">
+      <c r="AJ42"/>
+      <c r="AK42" s="13" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="AL43" s="19">
+      <c r="AL42" s="19">
         <v>124</v>
       </c>
-      <c r="AM43" s="13" t="inlineStr">
+      <c r="AM42" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN43" s="13"/>
-      <c r="AO43" s="13"/>
-      <c r="AP43" s="4"/>
-      <c r="AQ43" s="19">
+      <c r="AN42" s="13"/>
+      <c r="AO42" s="13"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="19">
         <v>10</v>
       </c>
-      <c r="AR43" s="19">
+      <c r="AR42" s="19">
         <v>1</v>
       </c>
-      <c r="AS43" s="14" t="inlineStr">
+      <c r="AS42" s="14" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="AT43" s="13" t="inlineStr">
+      <c r="AT42" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU43" s="13"/>
-      <c r="AV43" s="14"/>
-      <c r="AW43" s="13"/>
-      <c r="AX43" s="13"/>
-      <c r="AY43" s="13"/>
-      <c r="AZ43" s="13" t="inlineStr">
+      <c r="AU42" s="13"/>
+      <c r="AV42" s="14"/>
+      <c r="AW42" s="13"/>
+      <c r="AX42" s="13"/>
+      <c r="AY42" s="13"/>
+      <c r="AZ42" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BA43" s="13" t="inlineStr">
+      <c r="BA42" s="13" t="inlineStr">
         <is>
           <t>Recycled materials (Global Recycled Standard)
 Safer chemicals (Global Recycled Standard)
 Worker well-being (Global Recycled Standard)</t>
         </is>
       </c>
-      <c r="BB43" s="13"/>
-      <c r="BC43" s="13" t="inlineStr">
+      <c r="BB42" s="13"/>
+      <c r="BC42" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD43" s="13" t="inlineStr">
+      <c r="BD42" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE43" s="13"/>
-      <c r="BF43" s="13" t="inlineStr">
+      <c r="BE42" s="13"/>
+      <c r="BF42" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG43" s="13"/>
-      <c r="BH43" s="14"/>
-      <c r="BI43" s="23"/>
-      <c r="BJ43" s="23" t="inlineStr">
+      <c r="BG42" s="13"/>
+      <c r="BH42" s="14"/>
+      <c r="BI42" s="23"/>
+      <c r="BJ42" s="23" t="inlineStr">
         <is>
           <t>4.1 kg</t>
         </is>
       </c>
-      <c r="BK43" s="23" t="inlineStr">
+      <c r="BK42" s="23" t="inlineStr">
         <is>
           <t>4.10 kg</t>
         </is>
       </c>
-      <c r="BL43" s="23" t="inlineStr">
+      <c r="BL42" s="23" t="inlineStr">
         <is>
           <t>25.7L x 24.5W x 116.5H centimetres</t>
         </is>
       </c>
-      <c r="BM43" s="23"/>
-      <c r="BN43" s="23" t="inlineStr">
+      <c r="BM42" s="23"/>
+      <c r="BN42" s="23" t="inlineStr">
         <is>
           <t>4.1 kg</t>
         </is>
       </c>
-      <c r="BO43" s="23" t="inlineStr">
+      <c r="BO42" s="23" t="inlineStr">
         <is>
           <t>4.10 kg</t>
         </is>
       </c>
-      <c r="BP43" s="23" t="inlineStr">
+      <c r="BP42" s="23" t="inlineStr">
         <is>
           <t>44.5 x 32.9 x 19.4 cm</t>
         </is>
       </c>
-      <c r="BQ43" s="23" t="inlineStr">
+      <c r="BQ42" s="23" t="inlineStr">
         <is>
           <t>44.50 x 32.90 x 19.40 cm</t>
         </is>
       </c>
-      <c r="BR43" s="13" t="inlineStr">
+      <c r="BR42" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13">
-        <v>43</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14" t="inlineStr">
+    <row r="43" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13">
+        <v>42</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>B0HGLVYWYL</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>Colour Name: Deep Blue</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>Brand: SunSare | Special feature: 23-70 Minutes ➤ 650W Upgraded Motor ➤ 55kPa ➤ Auto Modes ➤ 1m Hose ➤ Removable Battery-Fully Charged Within 4 Hours ➤ Flexible Bending Adapter ➤ Wall-mounted Charging ➤ Aromatherapy Function ➤ Low Noise (≤ 62 db) ➤ Self-standing Design ➤ Intelligent High-Definition Display Screen ➤ V-Shaped Brush ➤ Large-Capacity Dust Cup (1.6 L) ➤ Dust Scraper | Filter type: HEPA Filter | Surface recommendation: All floors | Power source: Battery Powered</t>
         </is>
       </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>SunSare</t>
         </is>
       </c>
-      <c r="G44" s="14" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0HGLVYWYL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>Cordless Vacuum Cleaner, 650W 55KPa 70Mins Stick Vacuum with 90° Curved Adapter, 1m Hose, Aromatherapy, Wall-Mounted Charging, Touch Screen Auto Mode, Powerful Vacuum for Pet Hair/Carpets/Hardwood</t>
         </is>
       </c>
-      <c r="I44" s="14" t="inlineStr">
+      <c r="I43" s="14" t="inlineStr">
         <is>
           <t>【Powerful 650W Motor &amp; 55kPa Suction】– Equipped with a high-performance, ultra-quiet brushless 650W motor, the SunSare X13 cordless vacuum cleaner delivers up to 55kPa strong suction to capture fine dust and stubborn debris, even deep within carpet fibres. Improved noise reduction (&lt; 62 dB) ensures quiet, efficient cleaning—ideal for homes with pets and children.
 【Up to 70 Minutes Runtime &amp; Wall Charging】– The advanced high-capacity battery provides up to 70 minutes in Eco mode and 23 minutes on Max mode, allowing whole-home cleaning without frequent recharging. An optional backup battery can extend runtime to 140 minutes! The wall-mounted charging dock offers easy storage and automatic charging – simply place the vacuum on the mount and it starts charging instantly.
@@ -19020,244 +18736,244 @@
 【3 Years No-Worry Service】SunSare is committed to a customer-first approach, offering high-quality products and service. This vacuum comes with a 2-year free protection support. If any issues arise, contact us via the Brand Service Center or “Your Orders – Find the Item– Contact Seller – Choose a Reason – Write Your Message” We're always here to help!</t>
         </is>
       </c>
-      <c r="J44" s="14" t="inlineStr">
+      <c r="J43" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/dp/B0HGLVYWYL?psc=1</t>
         </is>
       </c>
-      <c r="K44" s="14" t="inlineStr">
+      <c r="K43" s="14" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/71qeciA31bL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L44" s="14" t="inlineStr">
+      <c r="L43" s="14" t="inlineStr">
         <is>
           <t>B0HHF6Q7N4</t>
         </is>
       </c>
-      <c r="M44" s="14" t="inlineStr">
+      <c r="M43" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="N44" s="14" t="inlineStr">
+      <c r="N43" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O44" s="15">
+      <c r="O43" s="15">
         <v>15554</v>
       </c>
-      <c r="P44" s="15">
+      <c r="P43" s="15">
         <v>-19309</v>
       </c>
-      <c r="Q44" s="16">
+      <c r="Q43" s="16">
         <v>-0.81</v>
       </c>
-      <c r="R44" s="17" t="inlineStr">
+      <c r="R43" s="17" t="inlineStr">
         <is>
           <t>Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="S44" s="18" t="inlineStr">
+      <c r="S43" s="18" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="T44" s="15">
+      <c r="T43" s="15">
         <v>122</v>
       </c>
-      <c r="U44" s="16"/>
-      <c r="V44" s="15">
+      <c r="U43" s="16"/>
+      <c r="V43" s="15">
         <v>18299</v>
       </c>
-      <c r="W44" s="15"/>
-      <c r="X44" s="15"/>
-      <c r="Y44" s="19">
+      <c r="W43" s="15"/>
+      <c r="X43" s="15"/>
+      <c r="Y43" s="19">
         <v>1</v>
       </c>
-      <c r="Z44" s="20">
+      <c r="Z43" s="20">
         <v>149.99</v>
       </c>
-      <c r="AA44" s="4"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="2"/>
-      <c r="AD44" s="19">
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="2"/>
+      <c r="AD43" s="19">
         <v>49</v>
       </c>
-      <c r="AE44" s="15">
+      <c r="AE43" s="15">
         <v>13</v>
       </c>
-      <c r="AF44" s="21">
+      <c r="AF43" s="21">
         <v>5</v>
       </c>
-      <c r="AG44" s="22">
+      <c r="AG43" s="22">
         <v>0.1066</v>
       </c>
-      <c r="AH44" s="20">
+      <c r="AH43" s="20">
         <v>3.71</v>
       </c>
-      <c r="AI44" s="16">
+      <c r="AI43" s="16">
         <v>0.98</v>
       </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="13" t="inlineStr">
+      <c r="AJ43"/>
+      <c r="AK43" s="13" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AL44" s="19">
+      <c r="AL43" s="19">
         <v>26</v>
       </c>
-      <c r="AM44" s="13" t="inlineStr">
+      <c r="AM43" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN44" s="13"/>
-      <c r="AO44" s="13"/>
-      <c r="AP44" s="4"/>
-      <c r="AQ44" s="19">
+      <c r="AN43" s="13"/>
+      <c r="AO43" s="13"/>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="19">
         <v>10</v>
       </c>
-      <c r="AR44" s="19">
+      <c r="AR43" s="19">
         <v>1</v>
       </c>
-      <c r="AS44" s="14" t="inlineStr">
+      <c r="AS43" s="14" t="inlineStr">
         <is>
           <t>ZhouKuam</t>
         </is>
       </c>
-      <c r="AT44" s="13" t="inlineStr">
+      <c r="AT43" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU44" s="13" t="inlineStr">
+      <c r="AU43" s="13" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AV44" s="14" t="inlineStr">
+      <c r="AV43" s="14" t="inlineStr">
         <is>
           <t>深圳市 广东 518000 CN</t>
         </is>
       </c>
-      <c r="AW44" s="13" t="inlineStr">
+      <c r="AW43" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA</t>
         </is>
       </c>
-      <c r="AX44" s="13"/>
-      <c r="AY44" s="13" t="inlineStr">
+      <c r="AX43" s="13"/>
+      <c r="AY43" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ44" s="13"/>
-      <c r="BA44" s="13"/>
-      <c r="BB44" s="13"/>
-      <c r="BC44" s="13" t="inlineStr">
+      <c r="AZ43" s="13"/>
+      <c r="BA43" s="13"/>
+      <c r="BB43" s="13"/>
+      <c r="BC43" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD44" s="13" t="inlineStr">
+      <c r="BD43" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE44" s="13"/>
-      <c r="BF44" s="13" t="inlineStr">
+      <c r="BE43" s="13"/>
+      <c r="BF43" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG44" s="13"/>
-      <c r="BH44" s="14"/>
-      <c r="BI44" s="23" t="inlineStr">
+      <c r="BG43" s="13"/>
+      <c r="BH43" s="14"/>
+      <c r="BI43" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ44" s="23" t="inlineStr">
+      <c r="BJ43" s="23" t="inlineStr">
         <is>
           <t>2.5 Kilograms</t>
         </is>
       </c>
-      <c r="BK44" s="23" t="inlineStr">
+      <c r="BK43" s="23" t="inlineStr">
         <is>
           <t>2.50 kg</t>
         </is>
       </c>
-      <c r="BL44" s="23" t="inlineStr">
+      <c r="BL43" s="23" t="inlineStr">
         <is>
           <t>33L x 25W x 118H centimetres</t>
         </is>
       </c>
-      <c r="BM44" s="23"/>
-      <c r="BN44" s="23" t="inlineStr">
+      <c r="BM43" s="23"/>
+      <c r="BN43" s="23" t="inlineStr">
         <is>
           <t>2.88 kg</t>
         </is>
       </c>
-      <c r="BO44" s="23" t="inlineStr">
+      <c r="BO43" s="23" t="inlineStr">
         <is>
           <t>2.88 kg</t>
         </is>
       </c>
-      <c r="BP44" s="23" t="inlineStr">
+      <c r="BP43" s="23" t="inlineStr">
         <is>
           <t>43.5 x 33 x 19.1 cm</t>
         </is>
       </c>
-      <c r="BQ44" s="23" t="inlineStr">
+      <c r="BQ43" s="23" t="inlineStr">
         <is>
           <t>43.50 x 33.00 x 19.10 cm</t>
         </is>
       </c>
-      <c r="BR44" s="13" t="inlineStr">
+      <c r="BR43" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="13">
-        <v>44</v>
-      </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="14" t="inlineStr">
+    <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="13">
+        <v>43</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>B0H152Z6PN</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>Colour Name: Golden</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
         <is>
           <t>Brand: SunSare | Special feature: ➤ 600W Brushless Motor➤ 4 Suction Modes, MAX 50,000 Pa➤ Auto Mode➤ Up to 65 Minutes Runtime &amp; 4-Hour Charging➤ Smart Display Screen➤ 5-Series Self-Standing Floor Brush➤ Aromatherapy Function➤ Multi-Layer Advanced Filtration System➤ Wall Mount➤ Removable Battery➤ Adjustable Height (94 cm–118 cm)➤ 1.5L Dust Cup➤ One-Touch Emptying➤ Washable Filtration System➤ Accessories: 1M Extended Hose/Sofa Brush/Long Crevice Brush | Filter type: HEPA Filter, Multi-Stage Filtration System | Surface recommendation: Carpet, Hardwood Floors, Stairs, Sofa, Mattress, Car, Home Cleaning | Power source: Battery Powered</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="F44" s="14" t="inlineStr">
         <is>
           <t>SunSare</t>
         </is>
       </c>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0H152Z6PN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr">
+      <c r="H44" s="14" t="inlineStr">
         <is>
           <t>SunSare Cordless Vacuum Cleaner 600W 50KPa 65Mins, Cordless Stick Vacuum with Self-Standing, Aromatherapy, AUTO Mode, 1M Hose, Wall-Charging, Powerful Vacuum for Pet Hair/Carpets/Hardwood (X7A Pro)</t>
         </is>
       </c>
-      <c r="I45" s="14" t="inlineStr">
+      <c r="I44" s="14" t="inlineStr">
         <is>
           <t>🌀【600W 50KPA Powerful Suction】The X7A Pro cordless vacuum cleaner features a market-leading 600W brushless motor (2026 latest model), delivering up to 50KPa strong suction. Easily removes dust, debris, and pet hair from carpets, hardwood, and tiles. Its performance surpasses 95% of household vacuum cleaners, ensuring a thorough clean and a healthier home environment.
 🔋【65-Minute Extended Runtime &amp; Wall-Mount Charging】Powered by an 8-cell lithium-ion battery, this cordless vacuum delivers up to 65 minutes of runtime in ECO mode (15–20 minutes in MAX mode). The wall-mount charging dock fully recharges the vacuum in 4 hours, and an optional spare battery extends runtime up to 130 minutes!
@@ -19268,252 +18984,252 @@
 💌【3-Year Worry-Free Service 】 SunSare offers a 3-year protection plan and 24/7 customer support. If any issues arise, just contact us—we're always here to help. Give the X7A Pro cordless vacuum a try—we promise you won't be disappointed!</t>
         </is>
       </c>
-      <c r="J45" s="14" t="inlineStr">
+      <c r="J44" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/dp/B0H152Z6PN?psc=1</t>
         </is>
       </c>
-      <c r="K45" s="14" t="inlineStr">
+      <c r="K44" s="14" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/716ZMBwgZEL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L45" s="14" t="inlineStr">
+      <c r="L44" s="14" t="inlineStr">
         <is>
           <t>B0HJGPBHR4</t>
         </is>
       </c>
-      <c r="M45" s="14" t="inlineStr">
+      <c r="M44" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="N45" s="14" t="inlineStr">
+      <c r="N44" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O45" s="15">
+      <c r="O44" s="15">
         <v>15032</v>
       </c>
-      <c r="P45" s="15">
+      <c r="P44" s="15">
         <v>123631</v>
       </c>
-      <c r="Q45" s="16">
+      <c r="Q44" s="16">
         <v>0.89</v>
       </c>
-      <c r="R45" s="17" t="inlineStr">
+      <c r="R44" s="17" t="inlineStr">
         <is>
           <t>Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="S45" s="18" t="inlineStr">
+      <c r="S44" s="18" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="T45" s="15">
+      <c r="T44" s="15">
         <v>131</v>
       </c>
-      <c r="U45" s="16">
+      <c r="U44" s="16">
         <v>-0.49</v>
       </c>
-      <c r="V45" s="15">
+      <c r="V44" s="15">
         <v>13099</v>
       </c>
-      <c r="W45" s="15" t="inlineStr">
+      <c r="W44" s="15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="X45" s="15">
+      <c r="X44" s="15">
         <v>11965</v>
       </c>
-      <c r="Y45" s="19">
+      <c r="Y44" s="19">
         <v>1</v>
       </c>
-      <c r="Z45" s="20">
+      <c r="Z44" s="20">
         <v>99.99</v>
       </c>
-      <c r="AA45" s="4"/>
-      <c r="AB45" s="1"/>
-      <c r="AC45" s="2"/>
-      <c r="AD45" s="19">
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="2"/>
+      <c r="AD44" s="19">
         <v>137</v>
       </c>
-      <c r="AE45" s="15">
+      <c r="AE44" s="15">
         <v>0</v>
       </c>
-      <c r="AF45" s="21">
+      <c r="AF44" s="21">
         <v>4.6</v>
       </c>
-      <c r="AG45" s="22">
+      <c r="AG44" s="22">
         <v>0</v>
       </c>
-      <c r="AH45" s="20">
+      <c r="AH44" s="20">
         <v>3.71</v>
       </c>
-      <c r="AI45" s="16">
+      <c r="AI44" s="16">
         <v>0.96</v>
       </c>
-      <c r="AJ45"/>
-      <c r="AK45" s="13" t="inlineStr">
+      <c r="AJ44"/>
+      <c r="AK44" s="13" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="AL45" s="19">
+      <c r="AL44" s="19">
         <v>116</v>
       </c>
-      <c r="AM45" s="13" t="inlineStr">
+      <c r="AM44" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN45" s="13"/>
-      <c r="AO45" s="13"/>
-      <c r="AP45" s="4"/>
-      <c r="AQ45" s="19">
+      <c r="AN44" s="13"/>
+      <c r="AO44" s="13"/>
+      <c r="AP44" s="4"/>
+      <c r="AQ44" s="19">
         <v>8</v>
       </c>
-      <c r="AR45" s="19">
+      <c r="AR44" s="19">
         <v>2</v>
       </c>
-      <c r="AS45" s="14" t="inlineStr">
+      <c r="AS44" s="14" t="inlineStr">
         <is>
           <t>ZhouKuam</t>
         </is>
       </c>
-      <c r="AT45" s="13" t="inlineStr">
+      <c r="AT44" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU45" s="13" t="inlineStr">
+      <c r="AU44" s="13" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AV45" s="14" t="inlineStr">
+      <c r="AV44" s="14" t="inlineStr">
         <is>
           <t>深圳市 广东 518000 CN</t>
         </is>
       </c>
-      <c r="AW45" s="13" t="inlineStr">
+      <c r="AW44" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA</t>
         </is>
       </c>
-      <c r="AX45" s="13"/>
-      <c r="AY45" s="13" t="inlineStr">
+      <c r="AX44" s="13"/>
+      <c r="AY44" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ45" s="13"/>
-      <c r="BA45" s="13"/>
-      <c r="BB45" s="13"/>
-      <c r="BC45" s="13" t="inlineStr">
+      <c r="AZ44" s="13"/>
+      <c r="BA44" s="13"/>
+      <c r="BB44" s="13"/>
+      <c r="BC44" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13" t="inlineStr">
+      <c r="BD44" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE45" s="13"/>
-      <c r="BF45" s="13" t="inlineStr">
+      <c r="BE44" s="13"/>
+      <c r="BF44" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG45" s="13"/>
-      <c r="BH45" s="14"/>
-      <c r="BI45" s="23" t="inlineStr">
+      <c r="BG44" s="13"/>
+      <c r="BH44" s="14"/>
+      <c r="BI44" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ45" s="23" t="inlineStr">
+      <c r="BJ44" s="23" t="inlineStr">
         <is>
           <t>4 Kilograms</t>
         </is>
       </c>
-      <c r="BK45" s="23" t="inlineStr">
+      <c r="BK44" s="23" t="inlineStr">
         <is>
           <t>4.00 kg</t>
         </is>
       </c>
-      <c r="BL45" s="23" t="inlineStr">
+      <c r="BL44" s="23" t="inlineStr">
         <is>
           <t>33L x 19W x 44H centimetres</t>
         </is>
       </c>
-      <c r="BM45" s="23"/>
-      <c r="BN45" s="23" t="inlineStr">
+      <c r="BM44" s="23"/>
+      <c r="BN44" s="23" t="inlineStr">
         <is>
           <t>4.28 kg</t>
         </is>
       </c>
-      <c r="BO45" s="23" t="inlineStr">
+      <c r="BO44" s="23" t="inlineStr">
         <is>
           <t>4.28 kg</t>
         </is>
       </c>
-      <c r="BP45" s="23" t="inlineStr">
+      <c r="BP44" s="23" t="inlineStr">
         <is>
           <t>43.4 x 33.6 x 19.8 cm</t>
         </is>
       </c>
-      <c r="BQ45" s="23" t="inlineStr">
+      <c r="BQ44" s="23" t="inlineStr">
         <is>
           <t>43.40 x 33.60 x 19.80 cm</t>
         </is>
       </c>
-      <c r="BR45" s="13" t="inlineStr">
+      <c r="BR44" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="13">
-        <v>45</v>
-      </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="14" t="inlineStr">
+    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13">
+        <v>44</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>B0H2JDPP44</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>Colour Name: Red and Grey | Size Name: F02 Ultra</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>Brand: VACTechPro | Special feature: 600W/50KPa, Come with Sofa Brush, Self Standing Design, Triple Anti-Tangle System(Soft bristles+Silicone strips+Serrated silicone strips comb), Up to 70 Minutes Runtime | Filter type: HEPA Filter | Surface recommendation: Hard Floor, carpet, hardwood | Power source: Battery Powered</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>VACTechPro</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2JDPP44&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>VACTechPro Upgraded F02 Ultra Cordless Vacuum Cleaner, 50KPa/600W/70Mins</t>
         </is>
       </c>
-      <c r="I46" s="14" t="inlineStr">
+      <c r="I45" s="14" t="inlineStr">
         <is>
           <t>High-Performance 600W Brushless Motor System: Powered by a 600W HyperCore Pro brushless motor, this cordless vacuum delivers strong suction up to 50KPa for effective cleaning on carpets, hard floors, and tight spaces. The noise reduction technology keeps operation below 62dB for quieter cleaning, while the brushless motor design enhances durability and reduces maintenance needs.
 Triple Anti-Tangle System: The silicone strip gently taps the floor or carpet to loosen fine dust. The soft bristles sweep away the fine dust. The fixed upper comb, serrated silicone strip, and wide suction opening work together to effectively pick up and detangle pet hair. Ideal for households with pets and carpets. The rotating electric brush head offers greater flexibility, making it easy to clean under furniture and in tight spaces. The built-in green LED light improves visibility in low-light conditions.
@@ -19524,242 +19240,242 @@
 Self-Standing Design: This cordless vacuum cleaner features a self-standing design. You can let go of the handle whenever you need to take a break during cleaning, without having to lean it against a wall or find a specific spot for support. In addition, we will respond promptly with careful attention and practical support whenever needed.</t>
         </is>
       </c>
-      <c r="J46" s="14" t="inlineStr">
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/dp/B0H2JDPP44?psc=1</t>
         </is>
       </c>
-      <c r="K46" s="14" t="inlineStr">
+      <c r="K45" s="14" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/71lVAl0ef0L._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L46" s="14" t="inlineStr">
+      <c r="L45" s="14" t="inlineStr">
         <is>
           <t>B0HJ4P6C9L</t>
         </is>
       </c>
-      <c r="M46" s="14" t="inlineStr">
+      <c r="M45" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="N46" s="14" t="inlineStr">
+      <c r="N45" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O46" s="15">
+      <c r="O45" s="15">
         <v>4164</v>
       </c>
-      <c r="P46" s="15">
+      <c r="P45" s="15">
         <v>42928</v>
       </c>
-      <c r="Q46" s="16">
+      <c r="Q45" s="16">
         <v>0.88</v>
       </c>
-      <c r="R46" s="17" t="inlineStr">
+      <c r="R45" s="17" t="inlineStr">
         <is>
           <t>Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="S46" s="18" t="inlineStr">
+      <c r="S45" s="18" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="T46" s="15">
+      <c r="T45" s="15">
         <v>120</v>
       </c>
-      <c r="U46" s="16"/>
-      <c r="V46" s="15">
+      <c r="U45" s="16"/>
+      <c r="V45" s="15">
         <v>11999</v>
       </c>
-      <c r="W46" s="15" t="inlineStr">
+      <c r="W45" s="15" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="X46" s="15">
+      <c r="X45" s="15">
         <v>5444</v>
       </c>
-      <c r="Y46" s="19">
+      <c r="Y45" s="19">
         <v>4</v>
       </c>
-      <c r="Z46" s="20">
+      <c r="Z45" s="20">
         <v>99.99</v>
       </c>
-      <c r="AA46" s="4"/>
-      <c r="AB46" s="1"/>
-      <c r="AC46" s="2"/>
-      <c r="AD46" s="19">
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="2"/>
+      <c r="AD45" s="19">
         <v>24</v>
       </c>
-      <c r="AE46" s="15">
+      <c r="AE45" s="15">
         <v>0</v>
       </c>
-      <c r="AF46" s="21">
+      <c r="AF45" s="21">
         <v>5</v>
       </c>
-      <c r="AG46" s="22">
+      <c r="AG45" s="22">
         <v>0</v>
       </c>
-      <c r="AH46" s="20">
+      <c r="AH45" s="20">
         <v>3.71</v>
       </c>
-      <c r="AI46" s="16">
+      <c r="AI45" s="16">
         <v>0.96</v>
       </c>
-      <c r="AJ46"/>
-      <c r="AK46" s="13" t="inlineStr">
+      <c r="AJ45"/>
+      <c r="AK45" s="13" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AL46" s="19">
+      <c r="AL45" s="19">
         <v>27</v>
       </c>
-      <c r="AM46" s="13" t="inlineStr">
+      <c r="AM45" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN46" s="13"/>
-      <c r="AO46" s="13"/>
-      <c r="AP46" s="4"/>
-      <c r="AQ46" s="19">
+      <c r="AN45" s="13"/>
+      <c r="AO45" s="13"/>
+      <c r="AP45" s="4"/>
+      <c r="AQ45" s="19">
         <v>9</v>
       </c>
-      <c r="AR46" s="19">
+      <c r="AR45" s="19">
         <v>2</v>
       </c>
-      <c r="AS46" s="14" t="inlineStr">
+      <c r="AS45" s="14" t="inlineStr">
         <is>
           <t>CHUANGJIN FAZHAN</t>
         </is>
       </c>
-      <c r="AT46" s="13" t="inlineStr">
+      <c r="AT45" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU46" s="13" t="inlineStr">
+      <c r="AU45" s="13" t="inlineStr">
         <is>
           <t>CN(HK)</t>
         </is>
       </c>
-      <c r="AV46" s="14" t="inlineStr">
+      <c r="AV45" s="14" t="inlineStr">
         <is>
           <t>300 LOCKHART ROAD WAN CHAI, 999077 HK</t>
         </is>
       </c>
-      <c r="AW46" s="13" t="inlineStr">
+      <c r="AW45" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3O3PYUTF0LFO3</t>
         </is>
       </c>
-      <c r="AX46" s="13"/>
-      <c r="AY46" s="13"/>
-      <c r="AZ46" s="13"/>
-      <c r="BA46" s="13"/>
-      <c r="BB46" s="13"/>
-      <c r="BC46" s="13" t="inlineStr">
+      <c r="AX45" s="13"/>
+      <c r="AY45" s="13"/>
+      <c r="AZ45" s="13"/>
+      <c r="BA45" s="13"/>
+      <c r="BB45" s="13"/>
+      <c r="BC45" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD46" s="13" t="inlineStr">
+      <c r="BD45" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE46" s="13"/>
-      <c r="BF46" s="13" t="inlineStr">
+      <c r="BE45" s="13"/>
+      <c r="BF45" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG46" s="13"/>
-      <c r="BH46" s="14"/>
-      <c r="BI46" s="23"/>
-      <c r="BJ46" s="23" t="inlineStr">
+      <c r="BG45" s="13"/>
+      <c r="BH45" s="14"/>
+      <c r="BI45" s="23"/>
+      <c r="BJ45" s="23" t="inlineStr">
         <is>
           <t>3.8 Kilograms</t>
         </is>
       </c>
-      <c r="BK46" s="23" t="inlineStr">
+      <c r="BK45" s="23" t="inlineStr">
         <is>
           <t>3.80 kg</t>
         </is>
       </c>
-      <c r="BL46" s="23" t="inlineStr">
+      <c r="BL45" s="23" t="inlineStr">
         <is>
           <t>40L x 12W x 23H centimetres</t>
         </is>
       </c>
-      <c r="BM46" s="23"/>
-      <c r="BN46" s="23" t="inlineStr">
+      <c r="BM45" s="23"/>
+      <c r="BN45" s="23" t="inlineStr">
         <is>
           <t>3.92 kg</t>
         </is>
       </c>
-      <c r="BO46" s="23" t="inlineStr">
+      <c r="BO45" s="23" t="inlineStr">
         <is>
           <t>3.92 kg</t>
         </is>
       </c>
-      <c r="BP46" s="23" t="inlineStr">
+      <c r="BP45" s="23" t="inlineStr">
         <is>
           <t>44.3 x 27.8 x 19.5 cm</t>
         </is>
       </c>
-      <c r="BQ46" s="23" t="inlineStr">
+      <c r="BQ45" s="23" t="inlineStr">
         <is>
           <t>44.30 x 27.80 x 19.50 cm</t>
         </is>
       </c>
-      <c r="BR46" s="13" t="inlineStr">
+      <c r="BR45" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="13">
-        <v>46</v>
-      </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="14" t="inlineStr">
+    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13">
+        <v>45</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>B0GDXHXP6X</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>Set name: S12 Turbo</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>Brand: Akitas | Special feature: Bagless, Corded, HEPA, Lightweight, Portable | Filter type: HEPA Filter | Surface recommendation: Carpet | Power source: Corded Electric</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>Akitas</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/stores/Akitas/page/BE01E01C-FB27-4053-9F09-4CEDBCF3376A?lp_asin=B0GDXHXP6X&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="H46" s="14" t="inlineStr">
         <is>
           <t>Akitas S12 Turbo Corded Vacuum Cleaner 2 in 1 Handheld Stick With German Wessel Werk Head + Pet Turbo Head Light Weight</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="I46" s="14" t="inlineStr">
         <is>
           <t>Powerful 600W Digital Motor, 17 KPa Strong Suction Power
 True Cyclone HEPA Filtration System With Dual Exhaust , Delivering Optimal Filtering Efficiency
@@ -19768,248 +19484,248 @@
 Aluminum Telescope Tube, Lightweight , 5m Power Cord for extensive Reach</t>
         </is>
       </c>
-      <c r="J47" s="14" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/dp/B0GDXHXP6X?psc=1</t>
         </is>
       </c>
-      <c r="K47" s="14" t="inlineStr">
+      <c r="K46" s="14" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41oG1zr0tUL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L47" s="14" t="inlineStr">
+      <c r="L46" s="14" t="inlineStr">
         <is>
           <t>B0HCBMM8Q9</t>
         </is>
       </c>
-      <c r="M47" s="14" t="inlineStr">
+      <c r="M46" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="N47" s="14" t="inlineStr">
+      <c r="N46" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O47" s="15">
+      <c r="O46" s="15">
         <v>18714</v>
       </c>
-      <c r="P47" s="15">
+      <c r="P46" s="15">
         <v>-5437</v>
       </c>
-      <c r="Q47" s="16">
+      <c r="Q46" s="16">
         <v>-0.32</v>
       </c>
-      <c r="R47" s="17" t="inlineStr">
+      <c r="R46" s="17" t="inlineStr">
         <is>
           <t>Stick Vacuums &amp; Electric Brooms</t>
         </is>
       </c>
-      <c r="S47" s="18" t="inlineStr">
+      <c r="S46" s="18" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="T47" s="15">
+      <c r="T46" s="15">
         <v>294</v>
       </c>
-      <c r="U47" s="16">
+      <c r="U46" s="16">
         <v>-0.08</v>
       </c>
-      <c r="V47" s="15">
+      <c r="V46" s="15">
         <v>11757</v>
       </c>
-      <c r="W47" s="15" t="inlineStr">
+      <c r="W46" s="15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="X47" s="15">
+      <c r="X46" s="15">
         <v>3999</v>
       </c>
-      <c r="Y47" s="19">
+      <c r="Y46" s="19">
         <v>2</v>
       </c>
-      <c r="Z47" s="20">
+      <c r="Z46" s="20">
         <v>39.99</v>
       </c>
-      <c r="AA47" s="4"/>
-      <c r="AB47" s="1"/>
-      <c r="AC47" s="2"/>
-      <c r="AD47" s="19">
+      <c r="AA46" s="4"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="2"/>
+      <c r="AD46" s="19">
         <v>1336</v>
       </c>
-      <c r="AE47" s="15">
+      <c r="AE46" s="15">
         <v>17</v>
       </c>
-      <c r="AF47" s="21">
+      <c r="AF46" s="21">
         <v>4.1</v>
       </c>
-      <c r="AG47" s="22">
+      <c r="AG46" s="22">
         <v>0.057800000000000004</v>
       </c>
-      <c r="AH47" s="20">
+      <c r="AH46" s="20">
         <v>3.61</v>
       </c>
-      <c r="AI47" s="16">
+      <c r="AI46" s="16">
         <v>0.91</v>
       </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="13" t="inlineStr">
+      <c r="AJ46"/>
+      <c r="AK46" s="13" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AL47" s="19">
+      <c r="AL46" s="19">
         <v>165</v>
       </c>
-      <c r="AM47" s="13" t="inlineStr">
+      <c r="AM46" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN47" s="13"/>
-      <c r="AO47" s="13"/>
-      <c r="AP47" s="4"/>
-      <c r="AQ47" s="19">
+      <c r="AN46" s="13"/>
+      <c r="AO46" s="13"/>
+      <c r="AP46" s="4"/>
+      <c r="AQ46" s="19">
         <v>10</v>
       </c>
-      <c r="AR47" s="19">
+      <c r="AR46" s="19">
         <v>2</v>
       </c>
-      <c r="AS47" s="14" t="inlineStr">
+      <c r="AS46" s="14" t="inlineStr">
         <is>
           <t>Chelsea &amp; Co</t>
         </is>
       </c>
-      <c r="AT47" s="13" t="inlineStr">
+      <c r="AT46" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU47" s="13" t="inlineStr">
+      <c r="AU46" s="13" t="inlineStr">
         <is>
           <t>CN(HK)</t>
         </is>
       </c>
-      <c r="AV47" s="14" t="inlineStr">
+      <c r="AV46" s="14" t="inlineStr">
         <is>
           <t>Tin Hau Hong Kong 852 HK</t>
         </is>
       </c>
-      <c r="AW47" s="13" t="inlineStr">
+      <c r="AW46" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
         </is>
       </c>
-      <c r="AX47" s="13"/>
-      <c r="AY47" s="13" t="inlineStr">
+      <c r="AX46" s="13"/>
+      <c r="AY46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ47" s="13"/>
-      <c r="BA47" s="13"/>
-      <c r="BB47" s="13"/>
-      <c r="BC47" s="13" t="inlineStr">
+      <c r="AZ46" s="13"/>
+      <c r="BA46" s="13"/>
+      <c r="BB46" s="13"/>
+      <c r="BC46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD47" s="13"/>
-      <c r="BE47" s="13"/>
-      <c r="BF47" s="13" t="inlineStr">
+      <c r="BD46" s="13"/>
+      <c r="BE46" s="13"/>
+      <c r="BF46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG47" s="13"/>
-      <c r="BH47" s="14"/>
-      <c r="BI47" s="23" t="inlineStr">
+      <c r="BG46" s="13"/>
+      <c r="BH46" s="14"/>
+      <c r="BI46" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ47" s="23" t="inlineStr">
+      <c r="BJ46" s="23" t="inlineStr">
         <is>
           <t>3.26 kg</t>
         </is>
       </c>
-      <c r="BK47" s="23" t="inlineStr">
+      <c r="BK46" s="23" t="inlineStr">
         <is>
           <t>3.26 kg</t>
         </is>
       </c>
-      <c r="BL47" s="23" t="inlineStr">
+      <c r="BL46" s="23" t="inlineStr">
         <is>
           <t>25L x 15W x 97H centimetres</t>
         </is>
       </c>
-      <c r="BM47" s="23"/>
-      <c r="BN47" s="23" t="inlineStr">
+      <c r="BM46" s="23"/>
+      <c r="BN46" s="23" t="inlineStr">
         <is>
           <t>3.26 kg</t>
         </is>
       </c>
-      <c r="BO47" s="23" t="inlineStr">
+      <c r="BO46" s="23" t="inlineStr">
         <is>
           <t>3.26 kg</t>
         </is>
       </c>
-      <c r="BP47" s="23" t="inlineStr">
+      <c r="BP46" s="23" t="inlineStr">
         <is>
           <t>45.1 x 28.5 x 19.6 cm</t>
         </is>
       </c>
-      <c r="BQ47" s="23" t="inlineStr">
+      <c r="BQ46" s="23" t="inlineStr">
         <is>
           <t>45.10 x 28.50 x 19.60 cm</t>
         </is>
       </c>
-      <c r="BR47" s="13" t="inlineStr">
+      <c r="BR46" s="13" t="inlineStr">
         <is>
           <t>轻型标准大件</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="13">
-        <v>47</v>
-      </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="14" t="inlineStr">
+    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13">
+        <v>46</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>B0FGPM83WQ</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>Set name: Grey Cordless Vacuum Cleaner with 1x Rechargeable Battery</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>Brand: Vlihapy | Special feature: Cordless, Detachable Battery, HEPA, Headlight, Lightweight | Filter type: HEPA Filter | Surface recommendation: Hard Floors, Tiles, Wooden Floors, Multi surface | Power source: Battery Powered</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>Vlihapy</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>6 IN 1 Cordless Vacuum Cleaner 160W 15000PA Powerful Stick Vacuums &amp; Electric Brooms with LED, 3000mAh Rechargeable Battery, Self-Standing Lightweight Handheld Vacuum for Pet Hair/Carpets/Floors</t>
         </is>
       </c>
-      <c r="I48" s="14" t="inlineStr">
+      <c r="I47" s="14" t="inlineStr">
         <is>
           <t>Powerful and Long-lasting Suction: The vacuum cleaner cordless powerful is equipped with the latest upgraded brushless motor, delivering an impressive power output of 160W. Vacuum : 15000PA, Speed: 130000RPM. Choose different suction modes according to different scenarios to reduce power consumption. The stick vacuums &amp; electric brooms effortlessly removes dust, pet hair, and stubborn dirt from carpets, hardwood floors, and furniture surfaces.
 Decent Run Time and Detachable Battery: The cordless vacuum cleaner battery capacity has undergone a significant upgrade! Removable lithium-ion battery, 3000mAh large-capacity rechargeable battery provides 65 minutes of working time, and a single charge can clean the hygiene of the entire home. The battery has overcharge and short circuit protection functions to achieve safer and more efficient charging. Additionally, the battery can be easily detached with just one button press.
@@ -20020,19 +19736,231 @@
 Professional After-sales Team: The quality of the upright vacuum cleaner is guaranteed and if you need our help after receiving the upright vacuum cleaner, we are more than happy to provide a solution. Providing you with excellent service is what we should do.</t>
         </is>
       </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L47" s="14" t="inlineStr">
+        <is>
+          <t>B0HBPKX54H</t>
+        </is>
+      </c>
+      <c r="M47" s="14" t="inlineStr">
+        <is>
+          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
+        </is>
+      </c>
+      <c r="N47" s="14" t="inlineStr">
+        <is>
+          <t>Home &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="O47" s="15">
+        <v>18777</v>
+      </c>
+      <c r="P47" s="15">
+        <v>-5433</v>
+      </c>
+      <c r="Q47" s="16">
+        <v>-0.47</v>
+      </c>
+      <c r="R47" s="17" t="inlineStr">
+        <is>
+          <t>Stick Vacuums &amp; Electric Brooms</t>
+        </is>
+      </c>
+      <c r="S47" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="T47" s="15">
+        <v>360</v>
+      </c>
+      <c r="U47" s="16">
+        <v>0.47</v>
+      </c>
+      <c r="V47" s="15">
+        <v>11513</v>
+      </c>
+      <c r="W47" s="15" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="X47" s="15">
+        <v>12891</v>
+      </c>
+      <c r="Y47" s="19">
+        <v>4</v>
+      </c>
+      <c r="Z47" s="20">
+        <v>42.97</v>
+      </c>
+      <c r="AA47" s="4"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="19">
+        <v>33</v>
+      </c>
+      <c r="AE47" s="15">
+        <v>15</v>
+      </c>
+      <c r="AF47" s="21">
+        <v>4.4</v>
+      </c>
+      <c r="AG47" s="22">
+        <v>0.0417</v>
+      </c>
+      <c r="AH47" s="20"/>
+      <c r="AI47" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ47"/>
+      <c r="AK47" s="13" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AL47" s="19">
+        <v>444</v>
+      </c>
+      <c r="AM47" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN47" s="13"/>
+      <c r="AO47" s="13"/>
+      <c r="AP47" s="4"/>
+      <c r="AQ47" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR47" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS47" s="14" t="inlineStr">
+        <is>
+          <t>Treasuretool</t>
+        </is>
+      </c>
+      <c r="AT47" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU47" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV47" s="14" t="inlineStr">
+        <is>
+          <t>南通市 崇川区 江苏省 226014 CN</t>
+        </is>
+      </c>
+      <c r="AW47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827</t>
+        </is>
+      </c>
+      <c r="AX47" s="13"/>
+      <c r="AY47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AZ47" s="13"/>
+      <c r="BA47" s="13"/>
+      <c r="BB47" s="13"/>
+      <c r="BC47" s="13"/>
+      <c r="BD47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE47" s="13"/>
+      <c r="BF47" s="13"/>
+      <c r="BG47" s="13"/>
+      <c r="BH47" s="14"/>
+      <c r="BI47" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
+      <c r="BJ47" s="23"/>
+      <c r="BK47" s="23"/>
+      <c r="BL47" s="23" t="inlineStr">
+        <is>
+          <t>23.5L x 15W x 110H centimetres</t>
+        </is>
+      </c>
+      <c r="BM47" s="23"/>
+      <c r="BN47" s="23"/>
+      <c r="BO47" s="23"/>
+      <c r="BP47" s="23"/>
+      <c r="BQ47" s="23"/>
+      <c r="BR47" s="13"/>
+    </row>
+    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13">
+        <v>47</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>B07ZQH4T3T</t>
+        </is>
+      </c>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>Brand: JML | Special feature: Swivels 360 degrees, Back-saving elbow joint, 4-quad brush technology with super sliders, Cordless 45min battery life | Filter type: Disk | Surface recommendation: Carpet | Power source: Battery Powered</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>JML</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>JML Swivel Sweeper Cordless Vacuum Cleaner – Rechargeable Floor Sweeper</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>UPRIGHT VACUUM CLEANERS - The easy-to-grab, cordless 7.2V rechargeable battery-operated Swivel Sweeper delivers 45 minutes of continuous cleaning, a game-changer among upright vacuums
+360-DEGREE SWIVEL: Our electric carpet sweeper features a fully swivelling 360-degree head, allowing you to navigate around furniture and tight spaces for a thorough clean, and the unique elbow joint allows you to reach under furniture without bending
+HAND HELD AND LIGHTWEIGHT - Hand held vacuum cordless and lightweight. Weighing just 2lbs, this handheld vacuum cleaner is your go-to hand vacuum for quick and easy cleanups
+TOUCHLESS DIRT TRAY - The bagless vacuum cleaners have a touchless dirt tray for easy and hygienic emptying. The 4-quad brush technology ensures you capture every speck of dirt
+EASY STORAGE - The stick vacuum cleaner has a space-saving magnetic storage latch for ease. Part of the JML products range for high quality and amazing results. Home gadgets to make cleaning quicker and easier</t>
+        </is>
+      </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0HBPKX54H</t>
+          <t>B07ZQH4T3T</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -20046,13 +19974,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>18777</v>
+        <v>7643</v>
       </c>
       <c r="P48" s="15">
-        <v>-5433</v>
+        <v>1600</v>
       </c>
       <c r="Q48" s="16">
-        <v>-0.47</v>
+        <v>0.24</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -20061,17 +19989,17 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>360</v>
+        <v>407</v>
       </c>
       <c r="U48" s="16">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="V48" s="15">
-        <v>11513</v>
+        <v>6101</v>
       </c>
       <c r="W48" s="15" t="inlineStr">
         <is>
@@ -20079,41 +20007,45 @@
         </is>
       </c>
       <c r="X48" s="15">
-        <v>12891</v>
+        <v>5823</v>
       </c>
       <c r="Y48" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>42.97</v>
+        <v>14.99</v>
       </c>
       <c r="AA48" s="4"/>
       <c r="AB48" s="1"/>
-      <c r="AC48" s="2"/>
+      <c r="AC48" s="2">
+        <v>21</v>
+      </c>
       <c r="AD48" s="19">
-        <v>33</v>
+        <v>2417</v>
       </c>
       <c r="AE48" s="15">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AF48" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.0417</v>
-      </c>
-      <c r="AH48" s="20"/>
+        <v>0.0147</v>
+      </c>
+      <c r="AH48" s="20">
+        <v>3.4</v>
+      </c>
       <c r="AI48" s="16">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>444</v>
+        <v>2174</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
@@ -20124,14 +20056,14 @@
       <c r="AO48" s="13"/>
       <c r="AP48" s="4"/>
       <c r="AQ48" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR48" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Treasuretool</t>
+          <t>JML Direct</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
@@ -20141,17 +20073,17 @@
       </c>
       <c r="AU48" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>南通市 崇川区 江苏省 226014 CN</t>
+          <t>London London W4 5RU GB</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
@@ -20163,7 +20095,11 @@
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
-      <c r="BC48" s="13"/>
+      <c r="BC48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD48" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20178,19 +20114,47 @@
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ48" s="23"/>
-      <c r="BK48" s="23"/>
+      <c r="BJ48" s="23" t="inlineStr">
+        <is>
+          <t>2 Pounds</t>
+        </is>
+      </c>
+      <c r="BK48" s="23" t="inlineStr">
+        <is>
+          <t>907.18 g</t>
+        </is>
+      </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>23.5L x 15W x 110H centimetres</t>
+          <t>20L x 18W x 7H centimetres</t>
         </is>
       </c>
       <c r="BM48" s="23"/>
-      <c r="BN48" s="23"/>
-      <c r="BO48" s="23"/>
-      <c r="BP48" s="23"/>
-      <c r="BQ48" s="23"/>
-      <c r="BR48" s="13"/>
+      <c r="BN48" s="23" t="inlineStr">
+        <is>
+          <t>1.31 kg</t>
+        </is>
+      </c>
+      <c r="BO48" s="23" t="inlineStr">
+        <is>
+          <t>1.31 kg</t>
+        </is>
+      </c>
+      <c r="BP48" s="23" t="inlineStr">
+        <is>
+          <t>39.3 x 23.8 x 7.9 cm</t>
+        </is>
+      </c>
+      <c r="BQ48" s="23" t="inlineStr">
+        <is>
+          <t>39.30 x 23.80 x 7.90 cm</t>
+        </is>
+      </c>
+      <c r="BR48" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13">
@@ -20199,52 +20163,56 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B07ZQH4T3T</t>
-        </is>
-      </c>
-      <c r="D49" s="14"/>
+          <t>B0GPWGRYLZ</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Colour Name: Black</t>
+        </is>
+      </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>Brand: JML | Special feature: Swivels 360 degrees, Back-saving elbow joint, 4-quad brush technology with super sliders, Cordless 45min battery life | Filter type: Disk | Surface recommendation: Carpet | Power source: Battery Powered</t>
+          <t>Brand: VACLANY | Special feature: Compact, HEPA, Lightweight | Filter type: HEPA Filter | Surface recommendation: Hard Floor, Carpet | Voltage: 220 Volts (AC)</t>
         </is>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>JML</t>
+          <t>VACLANY</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0GPWGRYLZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>JML Swivel Sweeper Cordless Vacuum Cleaner – Rechargeable Floor Sweeper</t>
+          <t>6-in-1 Corded Vacuum Cleaner, 21KPa 600W Powerful Suction (Black)</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>UPRIGHT VACUUM CLEANERS - The easy-to-grab, cordless 7.2V rechargeable battery-operated Swivel Sweeper delivers 45 minutes of continuous cleaning, a game-changer among upright vacuums
-360-DEGREE SWIVEL: Our electric carpet sweeper features a fully swivelling 360-degree head, allowing you to navigate around furniture and tight spaces for a thorough clean, and the unique elbow joint allows you to reach under furniture without bending
-HAND HELD AND LIGHTWEIGHT - Hand held vacuum cordless and lightweight. Weighing just 2lbs, this handheld vacuum cleaner is your go-to hand vacuum for quick and easy cleanups
-TOUCHLESS DIRT TRAY - The bagless vacuum cleaners have a touchless dirt tray for easy and hygienic emptying. The 4-quad brush technology ensures you capture every speck of dirt
-EASY STORAGE - The stick vacuum cleaner has a space-saving magnetic storage latch for ease. Part of the JML products range for high quality and amazing results. Home gadgets to make cleaning quicker and easier</t>
+          <t>🌀【Powerful 600W Corded Vacuum】Fitted with a strong 600W motor, this corded vacuum cleaner delivers 21KPa powerful suction. It easily picks up pet hair, dust, cat litter and everyday messes, leaving your home spotless.
+🌀【Lightweight &amp; Convertible Design】This stick vacuum turns into a handheld hoover in seconds. The adjustable telescopic tube (42–64cm), crevice tool and 2-in-1 brush clean floors, stairs, sofas and tight corners easily. At just 1.9kg, it’s light and comfortable to use.
+🌀【Advanced Four-stage Filtration System】This vacuum cleaner comes with 2 HEPA filters and a 4-stage filtration system. It traps fine dust and allergens, runs quietly and blows out cleaner air. Great for homes with pets and sensitive noses.
+🌀【5m Long Power Cord】No battery worries with this corded hoover. The 5m long cable lets you clean big rooms without changing plugs all the time, so you can clean non‑stop with your vacuum cleaner corded.
+🌀【All‑Floor Brush &amp; 1L Dust Cup】The anti‑tangle floor brush works on carpets and hard floors. The 1L dust cup is easy to take off, empty and clean. Compact size fits most homes and flats.</t>
         </is>
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GPWGRYLZ?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/417dvVhehaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B07ZQH4T3T</t>
+          <t>B0H3KCBSV3</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -20258,13 +20226,13 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>7643</v>
+        <v>10838</v>
       </c>
       <c r="P49" s="15">
-        <v>1600</v>
+        <v>146424</v>
       </c>
       <c r="Q49" s="16">
-        <v>0.24</v>
+        <v>0.92</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -20273,63 +20241,55 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>407</v>
+        <v>117</v>
       </c>
       <c r="U49" s="16">
-        <v>0.54</v>
+        <v>0.14</v>
       </c>
       <c r="V49" s="15">
-        <v>6101</v>
-      </c>
-      <c r="W49" s="15" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="X49" s="15">
-        <v>5823</v>
-      </c>
+        <v>3509</v>
+      </c>
+      <c r="W49" s="15"/>
+      <c r="X49" s="15"/>
       <c r="Y49" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z49" s="20">
-        <v>14.99</v>
+        <v>29.99</v>
       </c>
       <c r="AA49" s="4"/>
       <c r="AB49" s="1"/>
-      <c r="AC49" s="2">
-        <v>21</v>
-      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" s="19">
-        <v>2417</v>
+        <v>65</v>
       </c>
       <c r="AE49" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF49" s="21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.0147</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="AH49" s="20">
-        <v>3.4</v>
+        <v>5.48</v>
       </c>
       <c r="AI49" s="16">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>2174</v>
+        <v>9</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
@@ -20339,15 +20299,13 @@
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49" s="4"/>
-      <c r="AQ49" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ49" s="19"/>
       <c r="AR49" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>JML Direct</t>
+          <t>VAC LAN LTD.</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
@@ -20362,12 +20320,12 @@
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>London London W4 5RU GB</t>
+          <t>PULBOROUGH RH20 3BX GB</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
@@ -20384,11 +20342,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD49" s="13"/>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
@@ -20400,43 +20354,43 @@
       </c>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>2 Pounds</t>
+          <t>3.04 kg</t>
         </is>
       </c>
       <c r="BK49" s="23" t="inlineStr">
         <is>
-          <t>907.18 g</t>
+          <t>3.04 kg</t>
         </is>
       </c>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>20L x 18W x 7H centimetres</t>
+          <t>3L x 3W x 3H millimetres</t>
         </is>
       </c>
       <c r="BM49" s="23"/>
       <c r="BN49" s="23" t="inlineStr">
         <is>
-          <t>1.31 kg</t>
+          <t>3.04 kg</t>
         </is>
       </c>
       <c r="BO49" s="23" t="inlineStr">
         <is>
-          <t>1.31 kg</t>
+          <t>3.04 kg</t>
         </is>
       </c>
       <c r="BP49" s="23" t="inlineStr">
         <is>
-          <t>39.3 x 23.8 x 7.9 cm</t>
+          <t>46.4 x 44.9 x 17.9 cm</t>
         </is>
       </c>
       <c r="BQ49" s="23" t="inlineStr">
         <is>
-          <t>39.30 x 23.80 x 7.90 cm</t>
+          <t>46.40 x 44.90 x 17.90 cm</t>
         </is>
       </c>
       <c r="BR49" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -20447,17 +20401,17 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0GPWGRYLZ</t>
+          <t>B0H41JBK9R</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>Colour Name: Black</t>
+          <t>Colour Name: Navy Blue</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Brand: VACLANY | Special feature: Compact, HEPA, Lightweight | Filter type: HEPA Filter | Surface recommendation: Hard Floor, Carpet | Voltage: 220 Volts (AC)</t>
+          <t>Brand: VACLANY | Filter type: HEPA Filter | Surface recommendation: Hard Floor, Carpet | Voltage: 220 Volts (AC) | Included components: 1×Cordless Vacuum Main Motor, 1×Power Adapter, 2×HEPA Filter, Crevice Tool</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -20467,36 +20421,36 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0GPWGRYLZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0H41JBK9R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>6-in-1 Corded Vacuum Cleaner, 21KPa 600W Powerful Suction (Black)</t>
+          <t>30KPa Cordless Vacuum Cleaner, Stick Vacuum Cleaner with Removable Battery, 3 Powerful Suction Modes, 45Mins Runtime Vacuum Cleaner, Lightweight, Anti-Tangle, Stick Vacuum for Home &amp; Small Apartments</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>🌀【Powerful 600W Corded Vacuum】Fitted with a strong 600W motor, this corded vacuum cleaner delivers 21KPa powerful suction. It easily picks up pet hair, dust, cat litter and everyday messes, leaving your home spotless.
-🌀【Lightweight &amp; Convertible Design】This stick vacuum turns into a handheld hoover in seconds. The adjustable telescopic tube (42–64cm), crevice tool and 2-in-1 brush clean floors, stairs, sofas and tight corners easily. At just 1.9kg, it’s light and comfortable to use.
-🌀【Advanced Four-stage Filtration System】This vacuum cleaner comes with 2 HEPA filters and a 4-stage filtration system. It traps fine dust and allergens, runs quietly and blows out cleaner air. Great for homes with pets and sensitive noses.
-🌀【5m Long Power Cord】No battery worries with this corded hoover. The 5m long cable lets you clean big rooms without changing plugs all the time, so you can clean non‑stop with your vacuum cleaner corded.
-🌀【All‑Floor Brush &amp; 1L Dust Cup】The anti‑tangle floor brush works on carpets and hard floors. The 1L dust cup is easy to take off, empty and clean. Compact size fits most homes and flats.</t>
+          <t>🌀【6 in 1 Cordless Vacuum Cleaner】Our vacuum cleaner is equipped with 300W motor and 30 Kpa suction power. Two identical extension tubes, crevice nozzles and square brushes can be plugged together as needed and easily converted into a handheld vacuum for seamless cleaning. Say goodbye to pet hair, coffee beans, grit, dust and more on hard floors and tiles and leave your home looking brand new.
+🌀【Up to 45 Minutes of Running Time】Thanks to the 2200mAh*7 battery, this cordless hoover features three suction modes that provide up to 45 minutes of run time. Three battery indicators let you know how long the battery lasts. This cordless vacuum cleaner helps you clean your home thoroughly with ease, perfect for family homes and small flats.
+🌀【Lightweight and Convenient Hoover】This lightweight cordless vacuum cleaner comes with an anti-tangle floor brush that stops hair from tangling around the roller—saving you the hassle of manual cleaning. The stick vacuum cleaner cordless weighs just 2kg and features a flexible, rotatable brush head for easier handling. A bright LED light cleans corners and dark areas for a deeper clean; a large 1.2-litre dust collection volume eliminates the need for frequent emptying. Its ergonomically designed handle enables easy one-handed use—this wireless hoover is light enough for smooth, stress-free use, no matter your cleaning needs.
+🌀【Advanced Filtration System】5-stage filtration system ensures effective and thorough cleaning, and the high-density protection system removes up to 99.97% of tiny dust particles as small as 0.3 microns. This cordless stick vacuum cleaner provides fresher, healthier air for your family and is more suitable for allergy sufferers. Includes two additional washable HEPA filters.
+🌀【Wall-Mounted Charging and Removable Battery】The powerful cordless hoover comes with a wall-mounted charging station. You can place the cordless hoover on the wall charging stand and have it fully charged in 4 hours. The wall mount also provides space for other accessories. And the removable battery can be charged separately, including on kitchen worktops, or directly on the main unit.</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GPWGRYLZ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H41JBK9R?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/417dvVhehaL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51QKuTqDzeL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0H3KCBSV3</t>
+          <t>B0HK7MTKT1</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -20510,13 +20464,11 @@
         </is>
       </c>
       <c r="O50" s="15">
-        <v>10838</v>
-      </c>
-      <c r="P50" s="15">
-        <v>146424</v>
-      </c>
+        <v>11716</v>
+      </c>
+      <c r="P50" s="15"/>
       <c r="Q50" s="16">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="R50" s="17" t="inlineStr">
         <is>
@@ -20525,46 +20477,44 @@
       </c>
       <c r="S50" s="18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T50" s="15">
-        <v>117</v>
-      </c>
-      <c r="U50" s="16">
-        <v>0.14</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="U50" s="16"/>
       <c r="V50" s="15">
-        <v>3509</v>
+        <v>2280</v>
       </c>
       <c r="W50" s="15"/>
       <c r="X50" s="15"/>
       <c r="Y50" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z50" s="20">
-        <v>29.99</v>
+        <v>59.99</v>
       </c>
       <c r="AA50" s="4"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="2"/>
       <c r="AD50" s="19">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AE50" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AF50" s="21">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AG50" s="22">
-        <v>0.07690000000000001</v>
+        <v>0.1316</v>
       </c>
       <c r="AH50" s="20">
-        <v>5.48</v>
+        <v>3.71</v>
       </c>
       <c r="AI50" s="16">
-        <v>0.82</v>
+        <v>0.94</v>
       </c>
       <c r="AJ50"/>
       <c r="AK50" s="13" t="inlineStr">
@@ -20638,275 +20588,41 @@
       </c>
       <c r="BJ50" s="23" t="inlineStr">
         <is>
-          <t>3.04 kg</t>
+          <t>3.12 kg</t>
         </is>
       </c>
       <c r="BK50" s="23" t="inlineStr">
         <is>
-          <t>3.04 kg</t>
+          <t>3.12 kg</t>
         </is>
       </c>
       <c r="BL50" s="23" t="inlineStr">
         <is>
-          <t>3L x 3W x 3H millimetres</t>
+          <t>26L x 23W x 112H centimetres</t>
         </is>
       </c>
       <c r="BM50" s="23"/>
       <c r="BN50" s="23" t="inlineStr">
         <is>
-          <t>3.04 kg</t>
+          <t>3.12 kg</t>
         </is>
       </c>
       <c r="BO50" s="23" t="inlineStr">
         <is>
-          <t>3.04 kg</t>
+          <t>3.12 kg</t>
         </is>
       </c>
       <c r="BP50" s="23" t="inlineStr">
         <is>
-          <t>46.4 x 44.9 x 17.9 cm</t>
+          <t>44 x 32.3 x 18 cm</t>
         </is>
       </c>
       <c r="BQ50" s="23" t="inlineStr">
         <is>
-          <t>46.40 x 44.90 x 17.90 cm</t>
+          <t>44.00 x 32.30 x 18.00 cm</t>
         </is>
       </c>
       <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0H41JBK9R</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
-        <is>
-          <t>Colour Name: Navy Blue</t>
-        </is>
-      </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>Brand: VACLANY | Filter type: HEPA Filter | Surface recommendation: Hard Floor, Carpet | Voltage: 220 Volts (AC) | Included components: 1×Cordless Vacuum Main Motor, 1×Power Adapter, 2×HEPA Filter, Crevice Tool</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>VACLANY</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0H41JBK9R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>30KPa Cordless Vacuum Cleaner, Stick Vacuum Cleaner with Removable Battery, 3 Powerful Suction Modes, 45Mins Runtime Vacuum Cleaner, Lightweight, Anti-Tangle, Stick Vacuum for Home &amp; Small Apartments</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>🌀【6 in 1 Cordless Vacuum Cleaner】Our vacuum cleaner is equipped with 300W motor and 30 Kpa suction power. Two identical extension tubes, crevice nozzles and square brushes can be plugged together as needed and easily converted into a handheld vacuum for seamless cleaning. Say goodbye to pet hair, coffee beans, grit, dust and more on hard floors and tiles and leave your home looking brand new.
-🌀【Up to 45 Minutes of Running Time】Thanks to the 2200mAh*7 battery, this cordless hoover features three suction modes that provide up to 45 minutes of run time. Three battery indicators let you know how long the battery lasts. This cordless vacuum cleaner helps you clean your home thoroughly with ease, perfect for family homes and small flats.
-🌀【Lightweight and Convenient Hoover】This lightweight cordless vacuum cleaner comes with an anti-tangle floor brush that stops hair from tangling around the roller—saving you the hassle of manual cleaning. The stick vacuum cleaner cordless weighs just 2kg and features a flexible, rotatable brush head for easier handling. A bright LED light cleans corners and dark areas for a deeper clean; a large 1.2-litre dust collection volume eliminates the need for frequent emptying. Its ergonomically designed handle enables easy one-handed use—this wireless hoover is light enough for smooth, stress-free use, no matter your cleaning needs.
-🌀【Advanced Filtration System】5-stage filtration system ensures effective and thorough cleaning, and the high-density protection system removes up to 99.97% of tiny dust particles as small as 0.3 microns. This cordless stick vacuum cleaner provides fresher, healthier air for your family and is more suitable for allergy sufferers. Includes two additional washable HEPA filters.
-🌀【Wall-Mounted Charging and Removable Battery】The powerful cordless hoover comes with a wall-mounted charging station. You can place the cordless hoover on the wall charging stand and have it fully charged in 4 hours. The wall mount also provides space for other accessories. And the removable battery can be charged separately, including on kitchen worktops, or directly on the main unit.</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0H41JBK9R?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51QKuTqDzeL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HK7MTKT1</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>11716</v>
-      </c>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16">
-        <v>0</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>38</v>
-      </c>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15">
-        <v>2280</v>
-      </c>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>59.99</v>
-      </c>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>20</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>5</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.8</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0.1316</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>3.71</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.94</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>9</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>VAC LAN LTD.</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV51" s="14" t="inlineStr">
-        <is>
-          <t>PULBOROUGH RH20 3BX GB</t>
-        </is>
-      </c>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>3.12 kg</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>3.12 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>26L x 23W x 112H centimetres</t>
-        </is>
-      </c>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>3.12 kg</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>3.12 kg</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>44 x 32.3 x 18 cm</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>44.00 x 32.30 x 18.00 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
@@ -21202,102 +20918,95 @@
     <hyperlink ref="M39" r:id="rId284" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N39" r:id="rId285"/>
     <hyperlink ref="AW39" r:id="rId286" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TL6V3PPJTQHJ"/>
-    <hyperlink ref="C40" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
-    <hyperlink ref="G40" r:id="rId288" tooltip="https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0F9YPP9C3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId289" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1"/>
-    <hyperlink ref="K40" r:id="rId290" tooltip="https://images-na.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId291" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
+    <hyperlink ref="C40" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
+    <hyperlink ref="G40" r:id="rId288" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J40" r:id="rId289" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1"/>
+    <hyperlink ref="K40" r:id="rId290" tooltip="https://m.media-amazon.com/images/I/41LbZ7ZgbSL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId291" tooltip="https://www.amazon.co.uk/dp/B0HJ532G15"/>
     <hyperlink ref="M40" r:id="rId292" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N40" r:id="rId293"/>
-    <hyperlink ref="C41" r:id="rId294" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
-    <hyperlink ref="G41" r:id="rId295" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J41" r:id="rId296" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1"/>
-    <hyperlink ref="K41" r:id="rId297" tooltip="https://m.media-amazon.com/images/I/41LbZ7ZgbSL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId298" tooltip="https://www.amazon.co.uk/dp/B0HJ532G15"/>
-    <hyperlink ref="M41" r:id="rId299" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N41" r:id="rId300"/>
-    <hyperlink ref="AW41" r:id="rId301" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN"/>
-    <hyperlink ref="C42" r:id="rId302" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
-    <hyperlink ref="G42" r:id="rId303" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J42" r:id="rId304" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1"/>
-    <hyperlink ref="K42" r:id="rId305" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId306" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
-    <hyperlink ref="M42" r:id="rId307" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N42" r:id="rId308"/>
-    <hyperlink ref="AW42" r:id="rId309" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
-    <hyperlink ref="C43" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1"/>
-    <hyperlink ref="G43" r:id="rId311" tooltip="https://www.amazon.co.uk/stores/PROSCENIC/page/9D6AA08D-8BCB-40F7-A698-933D705EEDDF?lp_asin=B0H1WC1PJ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId312" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1?psc=1"/>
-    <hyperlink ref="K43" r:id="rId313" tooltip="https://images-na.ssl-images-amazon.com/images/I/61xgSdYZzpL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId314" tooltip="https://www.amazon.co.uk/dp/B0HFJ14KF6"/>
+    <hyperlink ref="AW40" r:id="rId294" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN"/>
+    <hyperlink ref="C41" r:id="rId295" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
+    <hyperlink ref="G41" r:id="rId296" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J41" r:id="rId297" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1"/>
+    <hyperlink ref="K41" r:id="rId298" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId299" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
+    <hyperlink ref="M41" r:id="rId300" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N41" r:id="rId301"/>
+    <hyperlink ref="AW41" r:id="rId302" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
+    <hyperlink ref="C42" r:id="rId303" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1"/>
+    <hyperlink ref="G42" r:id="rId304" tooltip="https://www.amazon.co.uk/stores/PROSCENIC/page/9D6AA08D-8BCB-40F7-A698-933D705EEDDF?lp_asin=B0H1WC1PJ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J42" r:id="rId305" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1?psc=1"/>
+    <hyperlink ref="K42" r:id="rId306" tooltip="https://images-na.ssl-images-amazon.com/images/I/61xgSdYZzpL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId307" tooltip="https://www.amazon.co.uk/dp/B0HFJ14KF6"/>
+    <hyperlink ref="M42" r:id="rId308" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N42" r:id="rId309"/>
+    <hyperlink ref="C43" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL"/>
+    <hyperlink ref="G43" r:id="rId311" tooltip="https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0HGLVYWYL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J43" r:id="rId312" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL?psc=1"/>
+    <hyperlink ref="K43" r:id="rId313" tooltip="https://images-na.ssl-images-amazon.com/images/I/71qeciA31bL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId314" tooltip="https://www.amazon.co.uk/dp/B0HHF6Q7N4"/>
     <hyperlink ref="M43" r:id="rId315" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N43" r:id="rId316"/>
-    <hyperlink ref="C44" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL"/>
-    <hyperlink ref="G44" r:id="rId318" tooltip="https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0HGLVYWYL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J44" r:id="rId319" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL?psc=1"/>
-    <hyperlink ref="K44" r:id="rId320" tooltip="https://images-na.ssl-images-amazon.com/images/I/71qeciA31bL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId321" tooltip="https://www.amazon.co.uk/dp/B0HHF6Q7N4"/>
-    <hyperlink ref="M44" r:id="rId322" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N44" r:id="rId323"/>
-    <hyperlink ref="AW44" r:id="rId324" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA"/>
-    <hyperlink ref="C45" r:id="rId325" tooltip="https://www.amazon.co.uk/dp/B0H152Z6PN"/>
-    <hyperlink ref="G45" r:id="rId326" tooltip="https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0H152Z6PN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J45" r:id="rId327" tooltip="https://www.amazon.co.uk/dp/B0H152Z6PN?psc=1"/>
-    <hyperlink ref="K45" r:id="rId328" tooltip="https://images-na.ssl-images-amazon.com/images/I/716ZMBwgZEL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId329" tooltip="https://www.amazon.co.uk/dp/B0HJGPBHR4"/>
-    <hyperlink ref="M45" r:id="rId330" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N45" r:id="rId331"/>
-    <hyperlink ref="AW45" r:id="rId332" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA"/>
-    <hyperlink ref="C46" r:id="rId333" tooltip="https://www.amazon.co.uk/dp/B0H2JDPP44"/>
-    <hyperlink ref="G46" r:id="rId334" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2JDPP44&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J46" r:id="rId335" tooltip="https://www.amazon.co.uk/dp/B0H2JDPP44?psc=1"/>
-    <hyperlink ref="K46" r:id="rId336" tooltip="https://images-na.ssl-images-amazon.com/images/I/71lVAl0ef0L._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId337" tooltip="https://www.amazon.co.uk/dp/B0HJ4P6C9L"/>
-    <hyperlink ref="M46" r:id="rId338" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N46" r:id="rId339"/>
-    <hyperlink ref="AW46" r:id="rId340" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3O3PYUTF0LFO3"/>
-    <hyperlink ref="C47" r:id="rId341" tooltip="https://www.amazon.co.uk/dp/B0GDXHXP6X"/>
-    <hyperlink ref="G47" r:id="rId342" tooltip="https://www.amazon.co.uk/stores/Akitas/page/BE01E01C-FB27-4053-9F09-4CEDBCF3376A?lp_asin=B0GDXHXP6X&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId343" tooltip="https://www.amazon.co.uk/dp/B0GDXHXP6X?psc=1"/>
-    <hyperlink ref="K47" r:id="rId344" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41oG1zr0tUL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId345" tooltip="https://www.amazon.co.uk/dp/B0HCBMM8Q9"/>
-    <hyperlink ref="M47" r:id="rId346" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N47" r:id="rId347"/>
-    <hyperlink ref="AW47" r:id="rId348" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C48" r:id="rId349" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
-    <hyperlink ref="G48" r:id="rId350" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy"/>
-    <hyperlink ref="J48" r:id="rId351" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1"/>
-    <hyperlink ref="K48" r:id="rId352" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId353" tooltip="https://www.amazon.co.uk/dp/B0HBPKX54H"/>
-    <hyperlink ref="M48" r:id="rId354" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N48" r:id="rId355"/>
-    <hyperlink ref="AW48" r:id="rId356" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827"/>
-    <hyperlink ref="C49" r:id="rId357" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
-    <hyperlink ref="G49" r:id="rId358" tooltip="https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J49" r:id="rId359" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1"/>
-    <hyperlink ref="K49" r:id="rId360" tooltip="https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId361" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
-    <hyperlink ref="M49" r:id="rId362" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N49" r:id="rId363"/>
-    <hyperlink ref="AW49" r:id="rId364" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1"/>
-    <hyperlink ref="C50" r:id="rId365" tooltip="https://www.amazon.co.uk/dp/B0GPWGRYLZ"/>
-    <hyperlink ref="G50" r:id="rId366" tooltip="https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0GPWGRYLZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId367" tooltip="https://www.amazon.co.uk/dp/B0GPWGRYLZ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId368" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/417dvVhehaL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId369" tooltip="https://www.amazon.co.uk/dp/B0H3KCBSV3"/>
-    <hyperlink ref="M50" r:id="rId370" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N50" r:id="rId371"/>
-    <hyperlink ref="AW50" r:id="rId372" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN"/>
-    <hyperlink ref="C51" r:id="rId373" tooltip="https://www.amazon.co.uk/dp/B0H41JBK9R"/>
-    <hyperlink ref="G51" r:id="rId374" tooltip="https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0H41JBK9R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J51" r:id="rId375" tooltip="https://www.amazon.co.uk/dp/B0H41JBK9R?psc=1"/>
-    <hyperlink ref="K51" r:id="rId376" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QKuTqDzeL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId377" tooltip="https://www.amazon.co.uk/dp/B0HK7MTKT1"/>
-    <hyperlink ref="M51" r:id="rId378" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N51" r:id="rId379"/>
-    <hyperlink ref="AW51" r:id="rId380" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN"/>
+    <hyperlink ref="AW43" r:id="rId317" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA"/>
+    <hyperlink ref="C44" r:id="rId318" tooltip="https://www.amazon.co.uk/dp/B0H152Z6PN"/>
+    <hyperlink ref="G44" r:id="rId319" tooltip="https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0H152Z6PN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J44" r:id="rId320" tooltip="https://www.amazon.co.uk/dp/B0H152Z6PN?psc=1"/>
+    <hyperlink ref="K44" r:id="rId321" tooltip="https://images-na.ssl-images-amazon.com/images/I/716ZMBwgZEL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B0HJGPBHR4"/>
+    <hyperlink ref="M44" r:id="rId323" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N44" r:id="rId324"/>
+    <hyperlink ref="AW44" r:id="rId325" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA"/>
+    <hyperlink ref="C45" r:id="rId326" tooltip="https://www.amazon.co.uk/dp/B0H2JDPP44"/>
+    <hyperlink ref="G45" r:id="rId327" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2JDPP44&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J45" r:id="rId328" tooltip="https://www.amazon.co.uk/dp/B0H2JDPP44?psc=1"/>
+    <hyperlink ref="K45" r:id="rId329" tooltip="https://images-na.ssl-images-amazon.com/images/I/71lVAl0ef0L._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId330" tooltip="https://www.amazon.co.uk/dp/B0HJ4P6C9L"/>
+    <hyperlink ref="M45" r:id="rId331" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N45" r:id="rId332"/>
+    <hyperlink ref="AW45" r:id="rId333" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3O3PYUTF0LFO3"/>
+    <hyperlink ref="C46" r:id="rId334" tooltip="https://www.amazon.co.uk/dp/B0GDXHXP6X"/>
+    <hyperlink ref="G46" r:id="rId335" tooltip="https://www.amazon.co.uk/stores/Akitas/page/BE01E01C-FB27-4053-9F09-4CEDBCF3376A?lp_asin=B0GDXHXP6X&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J46" r:id="rId336" tooltip="https://www.amazon.co.uk/dp/B0GDXHXP6X?psc=1"/>
+    <hyperlink ref="K46" r:id="rId337" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41oG1zr0tUL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId338" tooltip="https://www.amazon.co.uk/dp/B0HCBMM8Q9"/>
+    <hyperlink ref="M46" r:id="rId339" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N46" r:id="rId340"/>
+    <hyperlink ref="AW46" r:id="rId341" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C47" r:id="rId342" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
+    <hyperlink ref="G47" r:id="rId343" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy"/>
+    <hyperlink ref="J47" r:id="rId344" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1"/>
+    <hyperlink ref="K47" r:id="rId345" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId346" tooltip="https://www.amazon.co.uk/dp/B0HBPKX54H"/>
+    <hyperlink ref="M47" r:id="rId347" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N47" r:id="rId348"/>
+    <hyperlink ref="AW47" r:id="rId349" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827"/>
+    <hyperlink ref="C48" r:id="rId350" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
+    <hyperlink ref="G48" r:id="rId351" tooltip="https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId352" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1"/>
+    <hyperlink ref="K48" r:id="rId353" tooltip="https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId354" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
+    <hyperlink ref="M48" r:id="rId355" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N48" r:id="rId356"/>
+    <hyperlink ref="AW48" r:id="rId357" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1"/>
+    <hyperlink ref="C49" r:id="rId358" tooltip="https://www.amazon.co.uk/dp/B0GPWGRYLZ"/>
+    <hyperlink ref="G49" r:id="rId359" tooltip="https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0GPWGRYLZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J49" r:id="rId360" tooltip="https://www.amazon.co.uk/dp/B0GPWGRYLZ?psc=1"/>
+    <hyperlink ref="K49" r:id="rId361" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/417dvVhehaL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId362" tooltip="https://www.amazon.co.uk/dp/B0H3KCBSV3"/>
+    <hyperlink ref="M49" r:id="rId363" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N49" r:id="rId364"/>
+    <hyperlink ref="AW49" r:id="rId365" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN"/>
+    <hyperlink ref="C50" r:id="rId366" tooltip="https://www.amazon.co.uk/dp/B0H41JBK9R"/>
+    <hyperlink ref="G50" r:id="rId367" tooltip="https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0H41JBK9R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J50" r:id="rId368" tooltip="https://www.amazon.co.uk/dp/B0H41JBK9R?psc=1"/>
+    <hyperlink ref="K50" r:id="rId369" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QKuTqDzeL._AC_US600_.jpg"/>
+    <hyperlink ref="L50" r:id="rId370" tooltip="https://www.amazon.co.uk/dp/B0HK7MTKT1"/>
+    <hyperlink ref="M50" r:id="rId371" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N50" r:id="rId372"/>
+    <hyperlink ref="AW50" r:id="rId373" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN"/>
   </hyperlinks>
-  <drawing r:id="rId381"/>
+  <drawing r:id="rId374"/>
 </worksheet>
 </file>
 
@@ -21356,18 +21065,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>10445</v>
+        <v>8401</v>
       </c>
       <c r="C2" s="15">
-        <v>1937267</v>
+        <v>1906627</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>185.47314504547631</v>
+        <v>226.9523866206404</v>
       </c>
       <c r="G2" s="22">
-        <v>0.23626410911805287</v>
+        <v>0.1992410767224001</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21388,7 +21097,7 @@
         <v>301.38003965631196</v>
       </c>
       <c r="G3" s="22">
-        <v>0.034223800583591577</v>
+        <v>0.035882841219020516</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21409,7 +21118,7 @@
         <v>79.28202658447313</v>
       </c>
       <c r="G4" s="22">
-        <v>0.11741952995996291</v>
+        <v>0.12311158543815962</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21430,7 +21139,7 @@
         <v>111.88278260869565</v>
       </c>
       <c r="G5" s="22">
-        <v>0.0650320070573865</v>
+        <v>0.06818451322186647</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21451,7 +21160,7 @@
         <v>159.990099009901</v>
       </c>
       <c r="G6" s="22">
-        <v>0.03655364292338664</v>
+        <v>0.03832562551879521</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21472,7 +21181,7 @@
         <v>257.99040511727077</v>
       </c>
       <c r="G7" s="22">
-        <v>0.021217399172114276</v>
+        <v>0.02224593857464722</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21493,7 +21202,7 @@
         <v>154.58819584171698</v>
       </c>
       <c r="G8" s="22">
-        <v>0.03372616435567418</v>
+        <v>0.03536108146567058</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21514,7 +21223,7 @@
         <v>61.177700348432055</v>
       </c>
       <c r="G9" s="22">
-        <v>0.08439458028908141</v>
+        <v>0.08848571089766394</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21535,7 +21244,7 @@
         <v>60.83004349280696</v>
       </c>
       <c r="G10" s="22">
-        <v>0.06761066751114027</v>
+        <v>0.07088817739831614</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21556,7 +21265,7 @@
         <v>137.7828793774319</v>
       </c>
       <c r="G11" s="22">
-        <v>0.029066479676084056</v>
+        <v>0.030475512866121192</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21577,7 +21286,7 @@
         <v>139.98959236773635</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0260806623085797</v>
+        <v>0.02734495434602158</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21598,7 +21307,7 @@
         <v>149.97555791710946</v>
       </c>
       <c r="G13" s="22">
-        <v>0.021285258657739375</v>
+        <v>0.022317087631922212</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21619,7 +21328,7 @@
         <v>99.9900826446281</v>
       </c>
       <c r="G14" s="22">
-        <v>0.02736999253545658</v>
+        <v>0.02869678643424641</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21640,7 +21349,7 @@
         <v>219.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.008663394331470967</v>
+        <v>0.009083362978773865</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21661,7 +21370,7 @@
         <v>179.9908256880734</v>
       </c>
       <c r="G16" s="22">
-        <v>0.009862245244181049</v>
+        <v>0.010340329657298707</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21682,7 +21391,7 @@
         <v>96.19524405506884</v>
       </c>
       <c r="G17" s="22">
-        <v>0.018073243004818024</v>
+        <v>0.018949365587572632</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21703,7 +21412,7 @@
         <v>67.99044585987261</v>
       </c>
       <c r="G18" s="22">
-        <v>0.014205252324187383</v>
+        <v>0.014893869322898138</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21724,7 +21433,7 @@
         <v>36.99021352313167</v>
       </c>
       <c r="G19" s="22">
-        <v>0.02542468728087041</v>
+        <v>0.026657180125696667</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21745,7 +21454,7 @@
         <v>61.98947368421052</v>
       </c>
       <c r="G20" s="22">
-        <v>0.01504218598023027</v>
+        <v>0.01577137436262303</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21766,7 +21475,7 @@
         <v>24.99029714978775</v>
       </c>
       <c r="G21" s="22">
-        <v>0.03730009726526273</v>
+        <v>0.03910826514882011</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21787,7 +21496,7 @@
         <v>32.99002493765586</v>
       </c>
       <c r="G22" s="22">
-        <v>0.027211653735664684</v>
+        <v>0.028530771967271433</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21808,7 +21517,7 @@
         <v>99.99132947976878</v>
       </c>
       <c r="G23" s="22">
-        <v>0.00782646067542808</v>
+        <v>0.008205857939048974</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21829,7 +21538,7 @@
         <v>124.10276679841897</v>
       </c>
       <c r="G24" s="22">
-        <v>0.005722816621050012</v>
+        <v>0.00600023716352425</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21850,7 +21559,7 @@
         <v>129.9915254237288</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0053382795358411185</v>
+        <v>0.0055970591722993</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21871,7 +21580,7 @@
         <v>109.98930481283422</v>
       </c>
       <c r="G26" s="22">
-        <v>0.0042299079372978355</v>
+        <v>0.004434957903474445</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21892,7 +21601,7 @@
         <v>31.980555555555554</v>
       </c>
       <c r="G27" s="22">
-        <v>0.008143138275011876</v>
+        <v>0.008537886872998933</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21913,7 +21622,7 @@
         <v>14.99017199017199</v>
       </c>
       <c r="G28" s="22">
-        <v>0.00920627021647176</v>
+        <v>0.009652555436973794</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21934,7 +21643,7 @@
         <v>37.348387096774196</v>
       </c>
       <c r="G29" s="22">
-        <v>0.0035060734239634466</v>
+        <v>0.0036760346258745405</v>
       </c>
     </row>
   </sheetData>
@@ -21998,18 +21707,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>19284</v>
+        <v>17240</v>
       </c>
       <c r="C2" s="15">
-        <v>3045114</v>
+        <v>3014474</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>157.90883634100808</v>
+        <v>174.85348027842227</v>
       </c>
       <c r="G2" s="22">
-        <v>0.43620077359813614</v>
+        <v>0.40886991580694887</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22030,7 +21739,7 @@
         <v>80.70362663495838</v>
       </c>
       <c r="G3" s="22">
-        <v>0.07609310321427763</v>
+        <v>0.07978180955769003</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22051,7 +21760,7 @@
         <v>159.990099009901</v>
       </c>
       <c r="G4" s="22">
-        <v>0.03655364292338664</v>
+        <v>0.03832562551879521</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22072,7 +21781,7 @@
         <v>318.50064184852374</v>
       </c>
       <c r="G5" s="22">
-        <v>0.017620846433984032</v>
+        <v>0.018475038539072692</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22093,7 +21802,7 @@
         <v>61.177700348432055</v>
       </c>
       <c r="G6" s="22">
-        <v>0.08439458028908141</v>
+        <v>0.08848571089766394</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22114,7 +21823,7 @@
         <v>169.98968185726568</v>
       </c>
       <c r="G7" s="22">
-        <v>0.026306860593996697</v>
+        <v>0.027582117870271552</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22135,7 +21844,7 @@
         <v>60.83004349280696</v>
       </c>
       <c r="G8" s="22">
-        <v>0.06761066751114027</v>
+        <v>0.07088817739831614</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22156,7 +21865,7 @@
         <v>139.98959236773635</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0260806623085797</v>
+        <v>0.02734495434602158</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22177,7 +21886,7 @@
         <v>76.66447728516694</v>
       </c>
       <c r="G10" s="22">
-        <v>0.04132642674568527</v>
+        <v>0.04332977588046959</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22198,7 +21907,7 @@
         <v>99.9900826446281</v>
       </c>
       <c r="G11" s="22">
-        <v>0.02736999253545658</v>
+        <v>0.02869678643424641</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22219,7 +21928,7 @@
         <v>289.0</v>
       </c>
       <c r="G12" s="22">
-        <v>0.007871700332511479</v>
+        <v>0.008253290643898969</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22240,7 +21949,7 @@
         <v>149.96951219512195</v>
       </c>
       <c r="G13" s="22">
-        <v>0.014838607523354972</v>
+        <v>0.015557927190798055</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22261,7 +21970,7 @@
         <v>179.9908256880734</v>
       </c>
       <c r="G14" s="22">
-        <v>0.009862245244181049</v>
+        <v>0.010340329657298707</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22282,7 +21991,7 @@
         <v>88.39019607843137</v>
       </c>
       <c r="G15" s="22">
-        <v>0.011536112556266824</v>
+        <v>0.012095339736748489</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22303,7 +22012,7 @@
         <v>149.98947368421054</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0064466511343844015</v>
+        <v>0.006759160441124155</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22324,7 +22033,7 @@
         <v>36.99021352313167</v>
       </c>
       <c r="G17" s="22">
-        <v>0.02542468728087041</v>
+        <v>0.026657180125696667</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22345,7 +22054,7 @@
         <v>24.99029714978775</v>
       </c>
       <c r="G18" s="22">
-        <v>0.03730009726526273</v>
+        <v>0.03910826514882011</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22366,7 +22075,7 @@
         <v>99.99132947976878</v>
       </c>
       <c r="G19" s="22">
-        <v>0.00782646067542808</v>
+        <v>0.008205857939048974</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22387,7 +22096,7 @@
         <v>99.97865853658537</v>
       </c>
       <c r="G20" s="22">
-        <v>0.007419303761677486</v>
+        <v>0.007778963595399028</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22408,7 +22117,7 @@
         <v>124.10276679841897</v>
       </c>
       <c r="G21" s="22">
-        <v>0.005722816621050012</v>
+        <v>0.00600023716352425</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22429,7 +22138,7 @@
         <v>129.9915254237288</v>
       </c>
       <c r="G22" s="22">
-        <v>0.0053382795358411185</v>
+        <v>0.0055970591722993</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22450,7 +22159,7 @@
         <v>31.980555555555554</v>
       </c>
       <c r="G23" s="22">
-        <v>0.008143138275011876</v>
+        <v>0.008537886872998933</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22471,7 +22180,7 @@
         <v>14.99017199017199</v>
       </c>
       <c r="G24" s="22">
-        <v>0.00920627021647176</v>
+        <v>0.009652555436973794</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22492,7 +22201,7 @@
         <v>37.348387096774196</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0035060734239634466</v>
+        <v>0.0036760346258745405</v>
       </c>
     </row>
   </sheetData>
